--- a/examples/example_continuous_errors_subgroups_results.xlsx
+++ b/examples/example_continuous_errors_subgroups_results.xlsx
@@ -442,21 +442,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU61"/>
+  <dimension ref="A1:AO61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22.7109375" customWidth="1" min="1" max="10"/>
     <col width="15.7109375" customWidth="1" min="11" max="12"/>
     <col width="22.7109375" customWidth="1" min="13" max="17"/>
     <col width="15.7109375" customWidth="1" min="18" max="19"/>
-    <col width="22.7109375" customWidth="1" min="20" max="24"/>
-    <col width="15.7109375" customWidth="1" min="25" max="26"/>
-    <col width="22.7109375" customWidth="1" min="27" max="31"/>
-    <col width="15.7109375" customWidth="1" min="32" max="33"/>
-    <col width="22.7109375" customWidth="1" min="34" max="38"/>
-    <col width="15.7109375" customWidth="1" min="39" max="40"/>
-    <col width="22.7109375" customWidth="1" min="41" max="45"/>
-    <col width="15.7109375" customWidth="1" min="46" max="47"/>
+    <col width="22.7109375" customWidth="1" min="20" max="22"/>
+    <col width="15.7109375" customWidth="1" min="23" max="24"/>
+    <col width="22.7109375" customWidth="1" min="25" max="29"/>
+    <col width="15.7109375" customWidth="1" min="30" max="31"/>
+    <col width="22.7109375" customWidth="1" min="32" max="34"/>
+    <col width="15.7109375" customWidth="1" min="35" max="36"/>
+    <col width="22.7109375" customWidth="1" min="37" max="39"/>
+    <col width="15.7109375" customWidth="1" min="40" max="41"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -572,125 +572,95 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>RMSE Diff 95% CI adj low</t>
+          <t>Boot (RMSE) p</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>RMSE Diff 95% CI adj high</t>
+          <t>Boot (RMSE) p_adj</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Boot (RMSE) p</t>
+          <t>MedAE Diff</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Boot (RMSE) p_adj</t>
+          <t>MedAE Diff 95% CI low</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>MedAE Diff</t>
+          <t>MedAE Diff 95% CI high</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>MedAE Diff 95% CI low</t>
+          <t>MedAE Diff 95% CI adj low</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>MedAE Diff 95% CI high</t>
+          <t>MedAE Diff 95% CI adj high</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>MedAE Diff 95% CI adj low</t>
+          <t>Boot (MedAE) p</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>MedAE Diff 95% CI adj high</t>
+          <t>Boot (MedAE) p_adj</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>Boot (MedAE) p</t>
+          <t>SD Diff</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>Boot (MedAE) p_adj</t>
+          <t>SD Diff 95% CI low</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>SD Diff</t>
+          <t>SD Diff 95% CI high</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>SD Diff 95% CI low</t>
+          <t>Morgan-Pitman (SD) p</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>SD Diff 95% CI high</t>
+          <t>Morgan-Pitman (SD) p_adj</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>SD Diff 95% CI adj low</t>
+          <t>McNemar Diff</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>SD Diff 95% CI adj high</t>
+          <t>McNemar Diff 95% CI low</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>Morgan-Pitman (SD) p</t>
+          <t>McNemar Diff 95% CI high</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>Morgan-Pitman (SD) p_adj</t>
+          <t>McNemar p</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
-        <is>
-          <t>McNemar Diff</t>
-        </is>
-      </c>
-      <c r="AP1" t="inlineStr">
-        <is>
-          <t>McNemar Diff 95% CI low</t>
-        </is>
-      </c>
-      <c r="AQ1" t="inlineStr">
-        <is>
-          <t>McNemar Diff 95% CI high</t>
-        </is>
-      </c>
-      <c r="AR1" t="inlineStr">
-        <is>
-          <t>McNemar Diff 95% CI adj low</t>
-        </is>
-      </c>
-      <c r="AS1" t="inlineStr">
-        <is>
-          <t>McNemar Diff 95% CI adj high</t>
-        </is>
-      </c>
-      <c r="AT1" t="inlineStr">
-        <is>
-          <t>McNemar p</t>
-        </is>
-      </c>
-      <c r="AU1" t="inlineStr">
         <is>
           <t>McNemar p_adj</t>
         </is>
@@ -770,78 +740,60 @@
         <v>0.01787937336349218</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.05856576544801699</v>
+        <v>0.3852</v>
       </c>
       <c r="X2" t="n">
-        <v>0.02781683152088923</v>
+        <v>0.3852</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.3852</v>
+        <v>-0.009999999999999953</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.3852</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.009999999999999953</v>
+        <v>0.03999999999999998</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08000000000000002</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.03999999999999998</v>
+        <v>0.06000000000000011</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.08000000000000002</v>
+        <v>0.6968</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.06000000000000011</v>
+        <v>0.844</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.6968</v>
+        <v>-0.01535687255151641</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.844</v>
+        <v>-0.05064189418206674</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0.01535687255151641</v>
+        <v>0.01876017330561083</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.05064189418206674</v>
+        <v>0.3894</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.01876017330561083</v>
+        <v>0.3894</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.05815433485882694</v>
+        <v>0.03448275862068961</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.02825025172545625</v>
+        <v>-0.01805205348027686</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.3894</v>
+        <v>0.08780487804878048</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.3894</v>
+        <v>0.204560421762222</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.03448275862068961</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-0.01805205348027686</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0.08780487804878048</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>-0.03189014549308666</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0.09762516046213096</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0.204560421762222</v>
-      </c>
-      <c r="AU2" t="n">
         <v>0.204560421762222</v>
       </c>
     </row>
@@ -919,78 +871,60 @@
         <v>-0.0419672383242247</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.1343146850892963</v>
+        <v>0.0004</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.03239054644227168</v>
+        <v>0.0008</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0004</v>
+        <v>-0.06</v>
       </c>
       <c r="Z3" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-0.009999999999999953</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-0.1280741611297382</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.008074161129738258</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.0392</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.09859999999999999</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-0.08300106659587148</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-0.124012759523577</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-0.04070333062114999</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>0.0008</v>
       </c>
-      <c r="AA3" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-0.009999999999999953</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>-0.1280741611297382</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0.008074161129738258</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0.0392</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0.09859999999999999</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>-0.08300106659587148</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>-0.124012759523577</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>-0.04070333062114999</v>
-      </c>
       <c r="AK3" t="n">
-        <v>-0.1324121069898527</v>
+        <v>0.0788177339901478</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.03081160526701515</v>
+        <v>0.01979710286299567</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.1380185633575464</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.0008</v>
+        <v>0.009022063055144957</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.0788177339901478</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0.01979710286299567</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0.1380185633575464</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0.005016331658291476</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0.1509315375982046</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0.009022063055144957</v>
-      </c>
-      <c r="AU3" t="n">
         <v>0.02706618916543487</v>
       </c>
     </row>
@@ -1068,78 +1002,60 @@
         <v>-0.02214090274061026</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.1237607966652774</v>
+        <v>0.0036</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.01197481543232409</v>
+        <v>0.0052</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0036</v>
+        <v>-0.05000000000000004</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0052</v>
+        <v>-0.11</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.05000000000000004</v>
+        <v>0.01000000000000001</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.11</v>
+        <v>-0.1230166690346137</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.01000000000000001</v>
+        <v>0.02301666903461358</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.1230166690346137</v>
+        <v>0.2012</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.02301666903461358</v>
+        <v>0.2164</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.2012</v>
+        <v>-0.06764419404435507</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.2164</v>
+        <v>-0.1119735373189496</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.06764419404435507</v>
+        <v>-0.0211188354296671</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.1119735373189496</v>
+        <v>0.005</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.0211188354296671</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0.1227389787054995</v>
+        <v>0.04433497536945818</v>
       </c>
       <c r="AL4" t="n">
-        <v>-0.009991811914109227</v>
+        <v>-0.01686950701356149</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.005</v>
+        <v>0.1050067237163814</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.1549785601955193</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.04433497536945818</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>-0.01686950701356149</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0.1050067237163814</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>-0.0304885234225776</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0.1172132467873379</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0.1549785601955193</v>
-      </c>
-      <c r="AU4" t="n">
         <v>0.204560421762222</v>
       </c>
     </row>
@@ -1217,78 +1133,60 @@
         <v>0.08380091829685227</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.1396788216727526</v>
+        <v>0.7464</v>
       </c>
       <c r="X5" t="n">
-        <v>0.107729520460603</v>
+        <v>0.9228</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.7464</v>
+        <v>0.01000000000000001</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.9228</v>
+        <v>-0.08000000000000002</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01000000000000001</v>
+        <v>0.09500000000000003</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.08000000000000002</v>
+        <v>-0.09734129388236519</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.09500000000000003</v>
+        <v>0.1173412938823652</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.09734129388236519</v>
+        <v>0.8336</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.1173412938823652</v>
+        <v>0.8766</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.8336</v>
+        <v>-0.01723977231617346</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.8766</v>
+        <v>-0.117765501818481</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.01723977231617346</v>
+        <v>0.08218194600946505</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.117765501818481</v>
+        <v>0.751</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.08218194600946505</v>
+        <v>0.9198</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.1403678540165528</v>
+        <v>-0.0434782608695653</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.1052342909195122</v>
+        <v>-0.1486789027833803</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.751</v>
+        <v>0.05714285714285714</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9198</v>
+        <v>0.4104456923623511</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.0434782608695653</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>-0.1486789027833803</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0.05714285714285714</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>-0.1741545893719806</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0.08108108108108114</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0.4104456923623511</v>
-      </c>
-      <c r="AU5" t="n">
         <v>0.8208913847247021</v>
       </c>
     </row>
@@ -1366,78 +1264,60 @@
         <v>0.06288154246470519</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.144290130626136</v>
+        <v>0.5024</v>
       </c>
       <c r="X6" t="n">
-        <v>0.08263711906375129</v>
+        <v>0.7744</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5024</v>
+        <v>-0.04000000000000004</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.7744</v>
+        <v>-0.145</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.04000000000000004</v>
+        <v>0.06999999999999995</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.145</v>
+        <v>-0.1700413668805986</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.06999999999999995</v>
+        <v>0.09004136688059849</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.1700413668805986</v>
+        <v>0.5732</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.09004136688059849</v>
+        <v>0.7028</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.5732</v>
+        <v>-0.03108205860070312</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.7028</v>
+        <v>-0.1262655503625984</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.03108205860070312</v>
+        <v>0.06957054598927924</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.1262655503625984</v>
+        <v>0.5556</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.06957054598927924</v>
+        <v>0.8274</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.1469898117459688</v>
+        <v>0.01449275362318836</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.08947643166486603</v>
+        <v>-0.1475963668586618</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.5556</v>
+        <v>0.1803392531876139</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.8274</v>
+        <v>0.8633641527524397</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.01449275362318836</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>-0.1475963668586618</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0.1803392531876139</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>-0.1818181818181818</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0.2205882352941176</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0.8633641527524397</v>
-      </c>
-      <c r="AU6" t="n">
         <v>0.8633641527524397</v>
       </c>
     </row>
@@ -1515,78 +1395,60 @@
         <v>0.100814865669678</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.1614748457486424</v>
+        <v>0.8066</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1308031113881423</v>
+        <v>0.9228</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.8066</v>
+        <v>-0.05000000000000004</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.9228</v>
+        <v>-0.17</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.05000000000000004</v>
+        <v>0.06</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.17</v>
+        <v>-0.1850000000000001</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.06</v>
+        <v>0.08500000000000002</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.1850000000000001</v>
+        <v>0.4592</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.08500000000000002</v>
+        <v>0.6756</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.4592</v>
+        <v>-0.01384228628452966</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.6756</v>
+        <v>-0.1354366941567308</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.01384228628452966</v>
+        <v>0.1085662294439589</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.1354366941567308</v>
+        <v>0.8346</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.1085662294439589</v>
+        <v>0.9198</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0.1629424849920504</v>
+        <v>0.05797101449275366</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.1368814188906857</v>
+        <v>-0.07142857142857142</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.8346</v>
+        <v>0.1940298507462687</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.9198</v>
+        <v>0.3988546137823287</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.05797101449275366</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>-0.07142857142857142</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0.1940298507462687</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>-0.1050316598824059</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0.2277272727272732</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0.3988546137823287</v>
-      </c>
-      <c r="AU7" t="n">
         <v>0.7977092275646573</v>
       </c>
     </row>
@@ -1664,78 +1526,60 @@
         <v>0.02961214099715429</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.06924639598959506</v>
+        <v>0.503</v>
       </c>
       <c r="X8" t="n">
-        <v>0.04019670930361872</v>
+        <v>0.503</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.503</v>
+        <v>-0.04500000000000004</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.503</v>
+        <v>-0.105</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.04500000000000004</v>
+        <v>0.03999999999999998</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.105</v>
+        <v>-0.131897207526139</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.03999999999999998</v>
+        <v>0.04189720752613892</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.131897207526139</v>
+        <v>0.3164</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.04189720752613892</v>
+        <v>0.3292</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.3164</v>
+        <v>-0.01513592838370859</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.3292</v>
+        <v>-0.05940962551562724</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0.01513592838370859</v>
+        <v>0.02955483342924571</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0.05940962551562724</v>
+        <v>0.5008</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.02955483342924571</v>
+        <v>0.5008</v>
       </c>
       <c r="AK8" t="n">
-        <v>-0.06892480197736342</v>
+        <v>0.06302521008403361</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.04023956149928003</v>
+        <v>-0.008298755186721992</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.5008</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.5008</v>
+        <v>0.0785432549942764</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.06302521008403361</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>-0.008298755186721992</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>-0.0212179949513163</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0.1483633705869293</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0.0785432549942764</v>
-      </c>
-      <c r="AU8" t="n">
         <v>0.1570865099885528</v>
       </c>
     </row>
@@ -1813,78 +1657,60 @@
         <v>-0.03734422411782519</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.1735680846859624</v>
+        <v>0.0032</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.02302037088749732</v>
+        <v>0.0058</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0032</v>
+        <v>-0.08000000000000002</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0058</v>
+        <v>-0.16</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.08000000000000002</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.16</v>
+        <v>-0.1748543278868911</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>0.01485432788689105</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.1748543278868911</v>
+        <v>0.0716</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.01485432788689105</v>
+        <v>0.125</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.0716</v>
+        <v>-0.1005471804430421</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.125</v>
+        <v>-0.1598467389143226</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0.1005471804430421</v>
+        <v>-0.03791708938899847</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.1598467389143226</v>
+        <v>0.0042</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0.03791708938899847</v>
+        <v>0.0114</v>
       </c>
       <c r="AK9" t="n">
-        <v>-0.173472335352231</v>
+        <v>0.1008403361344539</v>
       </c>
       <c r="AL9" t="n">
-        <v>-0.02353042056685119</v>
+        <v>0.02574557059535602</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0042</v>
+        <v>0.1769547325102881</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.0114</v>
+        <v>0.01051393361055575</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.1008403361344539</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0.02574557059535602</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0.1769547325102881</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0.008498016588532281</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0.1965811965811965</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0.01051393361055575</v>
-      </c>
-      <c r="AU9" t="n">
         <v>0.03154180083166726</v>
       </c>
     </row>
@@ -1962,78 +1788,60 @@
         <v>-0.02545425540213038</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.157354026556972</v>
+        <v>0.0092</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.01043630456801225</v>
+        <v>0.0178</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0092</v>
+        <v>-0.03499999999999998</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.0178</v>
+        <v>-0.13</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.03499999999999998</v>
+        <v>0.04999999999999999</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.13</v>
+        <v>-0.145</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.04999999999999999</v>
+        <v>0.07500000000000001</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.145</v>
+        <v>0.454</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.07500000000000001</v>
+        <v>0.4868</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.454</v>
+        <v>-0.08541125205933353</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.4868</v>
+        <v>-0.1444532979412127</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0.08541125205933353</v>
+        <v>-0.0259623222200178</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.1444532979412127</v>
+        <v>0.0078</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0.0259623222200178</v>
+        <v>0.0204</v>
       </c>
       <c r="AK10" t="n">
-        <v>-0.1571408854458069</v>
+        <v>0.03781512605042026</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.009901327367602573</v>
+        <v>-0.04166666666666666</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.0078</v>
+        <v>0.1174456345342423</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.0204</v>
+        <v>0.3611297063274773</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.03781512605042026</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>-0.04166666666666666</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0.1174456345342423</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>-0.0595744680851064</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0.1346938775510204</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0.3611297063274773</v>
-      </c>
-      <c r="AU10" t="n">
         <v>0.3611297063274773</v>
       </c>
     </row>
@@ -2111,78 +1919,60 @@
         <v>0.06479860406880719</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.08248699381791254</v>
+        <v>0.8796</v>
       </c>
       <c r="X11" t="n">
-        <v>0.07690294037236957</v>
+        <v>0.8796</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.8796</v>
+        <v>-0.02000000000000002</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.8796</v>
+        <v>-0.145</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0.02000000000000002</v>
+        <v>0.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.145</v>
+        <v>-0.17</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.17</v>
+        <v>0.7403999999999999</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.13</v>
+        <v>0.757</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.7403999999999999</v>
+        <v>-0.0006221308517055935</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.757</v>
+        <v>-0.06607704412591212</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0.0006221308517055935</v>
+        <v>0.06891043687796762</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0.06607704412591212</v>
+        <v>0.9878</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.06891043687796762</v>
+        <v>0.9878</v>
       </c>
       <c r="AK11" t="n">
-        <v>-0.07990146932263836</v>
+        <v>0.05882352941176472</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.08197885824929078</v>
+        <v>-0.06172839506172839</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.9878</v>
+        <v>0.1739383215369061</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.9878</v>
+        <v>0.3521686283337344</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.05882352941176472</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>-0.06172839506172839</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0.1739383215369061</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>-0.08679783950617274</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0.1954022988505747</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0.3521686283337344</v>
-      </c>
-      <c r="AU11" t="n">
         <v>0.5097421176236591</v>
       </c>
     </row>
@@ -2260,78 +2050,60 @@
         <v>-0.008422926078273133</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.1693070518524953</v>
+        <v>0.0604</v>
       </c>
       <c r="X12" t="n">
-        <v>0.004803821189166998</v>
+        <v>0.1352</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.0604</v>
+        <v>-0.08000000000000002</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.1352</v>
+        <v>-0.16</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0.08000000000000002</v>
+        <v>0.03000000000000003</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.16</v>
+        <v>-0.1969638772366458</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.03000000000000003</v>
+        <v>0.03696387723664578</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0.1969638772366458</v>
+        <v>0.3068</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.03696387723664578</v>
+        <v>0.3108</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.3068</v>
+        <v>-0.06574117186796935</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.3108</v>
+        <v>-0.1300804816255988</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0.06574117186796935</v>
+        <v>-0.0005876934226714611</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0.1300804816255988</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0.0005876934226714611</v>
+        <v>0.198</v>
       </c>
       <c r="AK12" t="n">
-        <v>-0.1456654566829713</v>
+        <v>0.1058823529411764</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.01203820986317321</v>
+        <v>-0.01136363636363636</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.2207867713681667</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.198</v>
+        <v>0.06989330091427612</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.1058823529411764</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>-0.01136363636363636</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0.2207867713681667</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>-0.0365853658536585</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0.246964415395788</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0.06989330091427612</v>
-      </c>
-      <c r="AU12" t="n">
         <v>0.2096799027428284</v>
       </c>
     </row>
@@ -2409,78 +2181,60 @@
         <v>0.0144053794832945</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.1979869724170823</v>
+        <v>0.1694</v>
       </c>
       <c r="X13" t="n">
-        <v>0.03136522528973919</v>
+        <v>0.2644</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.1694</v>
+        <v>-0.06</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.2644</v>
+        <v>-0.17</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.06</v>
+        <v>0.09000000000000002</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.17</v>
+        <v>-0.2256336106560969</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.09000000000000002</v>
+        <v>0.1056336106560969</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.2256336106560969</v>
+        <v>0.6196</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.1056336106560969</v>
+        <v>0.622</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.6196</v>
+        <v>-0.06511904101626376</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.622</v>
+        <v>-0.1517479025259608</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0.06511904101626376</v>
+        <v>0.01388175857332033</v>
       </c>
       <c r="AI13" t="n">
-        <v>-0.1517479025259608</v>
+        <v>0.1478</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.01388175857332033</v>
+        <v>0.2254</v>
       </c>
       <c r="AK13" t="n">
-        <v>-0.1725524403691907</v>
+        <v>0.04705882352941171</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.03067357666807528</v>
+        <v>-0.08862165963431783</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.1478</v>
+        <v>0.1923308619091753</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.2254</v>
+        <v>0.5097421176236591</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.04705882352941171</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>-0.08862165963431783</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0.1923308619091753</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>-0.1115480649188513</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0.2282217477504961</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0.5097421176236591</v>
-      </c>
-      <c r="AU13" t="n">
         <v>0.5097421176236591</v>
       </c>
     </row>
@@ -2558,78 +2312,60 @@
         <v>0.1472807833189335</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.311327638423632</v>
+        <v>0.5392</v>
       </c>
       <c r="X14" t="n">
-        <v>0.1914378186031792</v>
+        <v>0.7336</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.5392</v>
+        <v>0.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.7336</v>
+        <v>-0.2999999999999999</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.1</v>
+        <v>0.3149999999999999</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.2999999999999999</v>
+        <v>-0.4070859156595976</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.3149999999999999</v>
+        <v>0.6070859156595976</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.4070859156595976</v>
+        <v>0.4472</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.6070859156595976</v>
+        <v>0.6702</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.4472</v>
+        <v>-0.05892506400629283</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.6702</v>
+        <v>-0.2405385039277502</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0.05892506400629283</v>
+        <v>0.1568253315184267</v>
       </c>
       <c r="AI14" t="n">
-        <v>-0.2405385039277502</v>
+        <v>0.5692</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.1568253315184267</v>
+        <v>0.7988</v>
       </c>
       <c r="AK14" t="n">
-        <v>-0.2790465669838161</v>
+        <v>-0.2142857142857144</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.2041490419357559</v>
+        <v>-0.5</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.5692</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.7988</v>
+        <v>0.1824114198766945</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.2142857142857144</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0.07692307692307693</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>-0.5833333333333334</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0.1538461538461539</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0.1824114198766945</v>
-      </c>
-      <c r="AU14" t="n">
         <v>0.4755952093831667</v>
       </c>
     </row>
@@ -2707,78 +2443,60 @@
         <v>0.04157097211756421</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.2372463099349515</v>
+        <v>0.2342</v>
       </c>
       <c r="X15" t="n">
-        <v>0.07899187056949331</v>
+        <v>0.4878</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.2342</v>
+        <v>0.13</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.4878</v>
+        <v>-0.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.13</v>
+        <v>0.1799999999999999</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.4</v>
+        <v>-0.3560526086581384</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.1799999999999999</v>
+        <v>0.6160526086581384</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.3560526086581384</v>
+        <v>0.6384</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.6160526086581384</v>
+        <v>0.6384</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.6384</v>
+        <v>-0.1026545673401243</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.6384</v>
+        <v>-0.2192857152597211</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0.1026545673401243</v>
+        <v>0.04860977532153791</v>
       </c>
       <c r="AI15" t="n">
-        <v>-0.2192857152597211</v>
+        <v>0.2212</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.04860977532153791</v>
+        <v>0.5102</v>
       </c>
       <c r="AK15" t="n">
-        <v>-0.2454668681387699</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.08248193350504243</v>
+        <v>-0.375</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.2212</v>
+        <v>0.1538461538461539</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.5102</v>
+        <v>0.3170634729221111</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.1428571428571428</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>-0.375</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0.1538461538461539</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>-0.4285714285714285</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0.1818181818181818</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0.3170634729221111</v>
-      </c>
-      <c r="AU15" t="n">
         <v>0.5851623225632632</v>
       </c>
     </row>
@@ -2856,78 +2574,60 @@
         <v>0.1240458422525336</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.2687390114133278</v>
+        <v>0.7804</v>
       </c>
       <c r="X16" t="n">
-        <v>0.1469604057978927</v>
+        <v>0.7804</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.7804</v>
+        <v>0.02999999999999997</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.7804</v>
+        <v>-0.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.02999999999999997</v>
+        <v>0.2200000000000001</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0.4</v>
+        <v>-0.4702498095020263</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.2200000000000001</v>
+        <v>0.5302498095020263</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0.4702498095020263</v>
+        <v>0.7816</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.5302498095020263</v>
+        <v>0.9528</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.7816</v>
+        <v>-0.04372950333383152</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.9528</v>
+        <v>-0.2080008716326983</v>
       </c>
       <c r="AH16" t="n">
-        <v>-0.04372950333383152</v>
+        <v>0.124937622244777</v>
       </c>
       <c r="AI16" t="n">
-        <v>-0.2080008716326983</v>
+        <v>0.6566</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.124937622244777</v>
+        <v>0.7988</v>
       </c>
       <c r="AK16" t="n">
-        <v>-0.2472378623407762</v>
+        <v>0.07142857142857151</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.1578671368505666</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.6566</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.7988</v>
+        <v>0.5851623225632632</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.07142857142857151</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>-0.1428571428571428</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0.3571428571428572</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>-0.1875</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0.5851623225632632</v>
-      </c>
-      <c r="AU16" t="n">
         <v>0.5851623225632632</v>
       </c>
     </row>
@@ -3005,78 +2705,60 @@
         <v>0.04683365584368027</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.1083550707159749</v>
+        <v>0.5008</v>
       </c>
       <c r="X17" t="n">
-        <v>0.06043735835439246</v>
+        <v>0.7176</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.5008</v>
+        <v>-0.004999999999999949</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.7176</v>
+        <v>-0.15</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.004999999999999949</v>
+        <v>0.09000000000000002</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0.15</v>
+        <v>-0.1729933913216897</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.09000000000000002</v>
+        <v>0.1629933913216898</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0.1729933913216897</v>
+        <v>0.8444</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.1629933913216898</v>
+        <v>0.9858</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.8444</v>
+        <v>-0.02404851818560094</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.9858</v>
+        <v>-0.09356784281214026</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0.02404851818560094</v>
+        <v>0.04691025066237122</v>
       </c>
       <c r="AI17" t="n">
-        <v>-0.09356784281214026</v>
+        <v>0.494</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.04691025066237122</v>
+        <v>0.7342</v>
       </c>
       <c r="AK17" t="n">
-        <v>-0.1086563941281395</v>
+        <v>0.0625</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.06197333125436442</v>
+        <v>-0.05633802816901409</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.494</v>
+        <v>0.1829758901037288</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.7342</v>
+        <v>0.3162826142201247</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>-0.05633802816901409</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0.1829758901037288</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>-0.08333333333333326</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0.2051282051282051</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0.3162826142201247</v>
-      </c>
-      <c r="AU17" t="n">
         <v>0.6760371945074246</v>
       </c>
     </row>
@@ -3154,78 +2836,60 @@
         <v>0.02816223503935631</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.1413278015852511</v>
+        <v>0.2758</v>
       </c>
       <c r="X18" t="n">
-        <v>0.04323238428178902</v>
+        <v>0.5276</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.2758</v>
+        <v>0.06</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.5276</v>
+        <v>-0.07024999999999942</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.06</v>
+        <v>0.105</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0.07024999999999942</v>
+        <v>-0.06493066111804412</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.105</v>
+        <v>0.1849306611180441</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0.06493066111804412</v>
+        <v>0.4948</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.1849306611180441</v>
+        <v>0.4948</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.4948</v>
+        <v>-0.03999438146030732</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.4948</v>
+        <v>-0.121100996345071</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0.03999438146030732</v>
+        <v>0.0327723377189352</v>
       </c>
       <c r="AI18" t="n">
-        <v>-0.121100996345071</v>
+        <v>0.3202</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.0327723377189352</v>
+        <v>0.5792</v>
       </c>
       <c r="AK18" t="n">
-        <v>-0.1399212818851053</v>
+        <v>0.01249999999999996</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.04949602724711644</v>
+        <v>-0.1081243894496906</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.3202</v>
+        <v>0.141025641025641</v>
       </c>
       <c r="AN18" t="n">
-        <v>0.5792</v>
+        <v>0.8428632884522782</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.01249999999999996</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>-0.1081243894496906</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0.141025641025641</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>-0.1302489177489176</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0.1688311688311689</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0.8428632884522782</v>
-      </c>
-      <c r="AU18" t="n">
         <v>0.8428632884522782</v>
       </c>
     </row>
@@ -3303,78 +2967,60 @@
         <v>0.06218517557437291</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.1208265528968928</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="X19" t="n">
-        <v>0.07898282591475339</v>
+        <v>0.7176</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.6578000000000001</v>
+        <v>0.06499999999999995</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.7176</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.06499999999999995</v>
+        <v>0.18</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.105010484337471</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.18</v>
+        <v>0.2350104843374709</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0.105010484337471</v>
+        <v>0.4752</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.2350104843374709</v>
+        <v>0.515</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.4752</v>
+        <v>-0.01594586327470637</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.515</v>
+        <v>-0.09981827999465605</v>
       </c>
       <c r="AH19" t="n">
-        <v>-0.01594586327470637</v>
+        <v>0.06649697059535598</v>
       </c>
       <c r="AI19" t="n">
-        <v>-0.09981827999465605</v>
+        <v>0.7156</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.06649697059535598</v>
+        <v>0.7342</v>
       </c>
       <c r="AK19" t="n">
-        <v>-0.120291009253404</v>
+        <v>-0.05000000000000004</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.08374599188502276</v>
+        <v>-0.1764705882352941</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.7156</v>
+        <v>0.08</v>
       </c>
       <c r="AN19" t="n">
-        <v>0.7342</v>
+        <v>0.4506914630049498</v>
       </c>
       <c r="AO19" t="n">
-        <v>-0.05000000000000004</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>-0.1764705882352941</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>-0.2105263157894737</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0.1036050156739813</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0.4506914630049498</v>
-      </c>
-      <c r="AU19" t="n">
         <v>0.8428632884522782</v>
       </c>
     </row>
@@ -3452,78 +3098,60 @@
         <v>0.003138483807388096</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.1584184428614014</v>
+        <v>0.067</v>
       </c>
       <c r="X20" t="n">
-        <v>0.02016397923086491</v>
+        <v>0.1292</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.067</v>
+        <v>-0.04499999999999998</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.1292</v>
+        <v>-0.185</v>
       </c>
       <c r="AA20" t="n">
-        <v>-0.04499999999999998</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AB20" t="n">
-        <v>-0.185</v>
+        <v>-0.1980776834094579</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1080776834094579</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0.1980776834094579</v>
+        <v>0.4908</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.1080776834094579</v>
+        <v>0.791</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.4908</v>
+        <v>-0.07205219427026116</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.791</v>
+        <v>-0.1421073178832891</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0.07205219427026116</v>
+        <v>0.004459795122010743</v>
       </c>
       <c r="AI20" t="n">
-        <v>-0.1421073178832891</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.004459795122010743</v>
+        <v>0.1534</v>
       </c>
       <c r="AK20" t="n">
-        <v>-0.1542146413536229</v>
+        <v>0.09999999999999998</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.02101114622127575</v>
+        <v>-0.02599111414900885</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="AN20" t="n">
-        <v>0.1534</v>
+        <v>0.1436999664939087</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.09999999999999998</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>-0.02599111414900885</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0.2307692307692308</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>-0.0609756097560975</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0.2631578947368421</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0.1436999664939087</v>
-      </c>
-      <c r="AU20" t="n">
         <v>0.2873999329878174</v>
       </c>
     </row>
@@ -3601,78 +3229,60 @@
         <v>-0.04161403684911791</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.2447806093301479</v>
+        <v>0.0176</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.02207038736559981</v>
+        <v>0.0442</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.0176</v>
+        <v>-0.04999999999999999</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.0442</v>
+        <v>-0.21</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0.04999999999999999</v>
+        <v>0.07499999999999996</v>
       </c>
       <c r="AB21" t="n">
-        <v>-0.21</v>
+        <v>-0.23</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.07499999999999996</v>
+        <v>0.13</v>
       </c>
       <c r="AD21" t="n">
-        <v>-0.23</v>
+        <v>0.5788</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.13</v>
+        <v>0.791</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.5788</v>
+        <v>-0.1379086175180185</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.791</v>
+        <v>-0.2273042548645464</v>
       </c>
       <c r="AH21" t="n">
-        <v>-0.1379086175180185</v>
+        <v>-0.0390321906264582</v>
       </c>
       <c r="AI21" t="n">
-        <v>-0.2273042548645464</v>
+        <v>0.013</v>
       </c>
       <c r="AJ21" t="n">
-        <v>-0.0390321906264582</v>
+        <v>0.0574</v>
       </c>
       <c r="AK21" t="n">
-        <v>-0.2477664215622339</v>
+        <v>0.15</v>
       </c>
       <c r="AL21" t="n">
-        <v>-0.01865676378003534</v>
+        <v>0.03703703703703703</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.013</v>
+        <v>0.2682926829268293</v>
       </c>
       <c r="AN21" t="n">
-        <v>0.0574</v>
+        <v>0.01223080235262762</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0.03703703703703703</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0.2682926829268293</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0.01234567901234562</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0.296646646646647</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0.01223080235262762</v>
-      </c>
-      <c r="AU21" t="n">
         <v>0.03669240705788286</v>
       </c>
     </row>
@@ -3750,78 +3360,60 @@
         <v>0.04279519956824287</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.1959462103310022</v>
+        <v>0.2766</v>
       </c>
       <c r="X22" t="n">
-        <v>0.06502125025034049</v>
+        <v>0.2766</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.2766</v>
+        <v>-0.005000000000000004</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.2766</v>
+        <v>-0.1602499999999994</v>
       </c>
       <c r="AA22" t="n">
-        <v>-0.005000000000000004</v>
+        <v>0.15</v>
       </c>
       <c r="AB22" t="n">
-        <v>-0.1602499999999994</v>
+        <v>-0.1926521416878366</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.15</v>
+        <v>0.1826521416878366</v>
       </c>
       <c r="AD22" t="n">
-        <v>-0.1926521416878366</v>
+        <v>1</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.1826521416878366</v>
+        <v>1</v>
       </c>
       <c r="AF22" t="n">
-        <v>1</v>
+        <v>-0.06585642324775731</v>
       </c>
       <c r="AG22" t="n">
-        <v>1</v>
+        <v>-0.1743855750586173</v>
       </c>
       <c r="AH22" t="n">
-        <v>-0.06585642324775731</v>
+        <v>0.0420199289689417</v>
       </c>
       <c r="AI22" t="n">
-        <v>-0.1743855750586173</v>
+        <v>0.2622</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.0420199289689417</v>
+        <v>0.2622</v>
       </c>
       <c r="AK22" t="n">
-        <v>-0.1967670115452185</v>
+        <v>0.05000000000000004</v>
       </c>
       <c r="AL22" t="n">
-        <v>0.06889649485977117</v>
+        <v>-0.1038961038961039</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.2622</v>
+        <v>0.1948051948051948</v>
       </c>
       <c r="AN22" t="n">
-        <v>0.2622</v>
+        <v>0.5075279756928801</v>
       </c>
       <c r="AO22" t="n">
-        <v>0.05000000000000004</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>-0.1038961038961039</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>0.1948051948051948</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>-0.1392405063291139</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>0.225583333333334</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0.5075279756928801</v>
-      </c>
-      <c r="AU22" t="n">
         <v>0.5075279756928801</v>
       </c>
     </row>
@@ -3899,78 +3491,60 @@
         <v>0.08588529649286161</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.1169046885201632</v>
+        <v>0.8912</v>
       </c>
       <c r="X23" t="n">
-        <v>0.1036320810743393</v>
+        <v>0.8912</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.8912</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.8912</v>
+        <v>-0.19</v>
       </c>
       <c r="AA23" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="AB23" t="n">
-        <v>-0.19</v>
+        <v>-0.23</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.08999999999999994</v>
       </c>
       <c r="AD23" t="n">
-        <v>-0.23</v>
+        <v>0.3276</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.08999999999999994</v>
+        <v>0.4882</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.3276</v>
+        <v>-0.01006570451090821</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.4882</v>
+        <v>-0.09837143988402267</v>
       </c>
       <c r="AH23" t="n">
-        <v>-0.01006570451090821</v>
+        <v>0.0805240817664126</v>
       </c>
       <c r="AI23" t="n">
-        <v>-0.09837143988402267</v>
+        <v>0.8372000000000001</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.0805240817664126</v>
+        <v>0.8372000000000001</v>
       </c>
       <c r="AK23" t="n">
-        <v>-0.1196438623098647</v>
+        <v>0.06024096385542166</v>
       </c>
       <c r="AL23" t="n">
-        <v>0.1015557952472973</v>
+        <v>-0.0625</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.8372000000000001</v>
+        <v>0.1818736141906876</v>
       </c>
       <c r="AN23" t="n">
-        <v>0.8372000000000001</v>
+        <v>0.3376355867918768</v>
       </c>
       <c r="AO23" t="n">
-        <v>0.06024096385542166</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>-0.0625</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>0.1818736141906876</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>-0.09024514811031653</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>0.2080119115144647</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>0.3376355867918768</v>
-      </c>
-      <c r="AU23" t="n">
         <v>0.4963912912556804</v>
       </c>
     </row>
@@ -4048,78 +3622,60 @@
         <v>0.04131613934753328</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.1857605197426813</v>
+        <v>0.2258</v>
       </c>
       <c r="X24" t="n">
-        <v>0.07124203167295236</v>
+        <v>0.4414</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.2258</v>
+        <v>-0.11</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.4414</v>
+        <v>-0.23</v>
       </c>
       <c r="AA24" t="n">
-        <v>-0.11</v>
+        <v>0.03525000000000088</v>
       </c>
       <c r="AB24" t="n">
-        <v>-0.23</v>
+        <v>-0.2724659647896756</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.03525000000000088</v>
+        <v>0.05246596478967558</v>
       </c>
       <c r="AD24" t="n">
-        <v>-0.2724659647896756</v>
+        <v>0.1188</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.05246596478967558</v>
+        <v>0.2406</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.1188</v>
+        <v>-0.06751957058679842</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.2406</v>
+        <v>-0.1653308669469955</v>
       </c>
       <c r="AH24" t="n">
-        <v>-0.06751957058679842</v>
+        <v>0.03715874739121014</v>
       </c>
       <c r="AI24" t="n">
-        <v>-0.1653308669469955</v>
+        <v>0.2366</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.03715874739121014</v>
+        <v>0.4854</v>
       </c>
       <c r="AK24" t="n">
-        <v>-0.1840609110439013</v>
+        <v>0.1084337349397589</v>
       </c>
       <c r="AL24" t="n">
-        <v>0.06269554011537042</v>
+        <v>-0.025</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.2366</v>
+        <v>0.2435897435897436</v>
       </c>
       <c r="AN24" t="n">
-        <v>0.4854</v>
+        <v>0.1171006486185413</v>
       </c>
       <c r="AO24" t="n">
-        <v>0.1084337349397589</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>-0.025</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>0.2435897435897436</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>-0.06199845679012332</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>0.2709440813362386</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>0.1171006486185413</v>
-      </c>
-      <c r="AU24" t="n">
         <v>0.351301945855624</v>
       </c>
     </row>
@@ -4197,78 +3753,60 @@
         <v>0.06369285960218346</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.1967235448779499</v>
+        <v>0.3374</v>
       </c>
       <c r="X25" t="n">
-        <v>0.09497646596266225</v>
+        <v>0.5282</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.3374</v>
+        <v>-0.03999999999999998</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.5282</v>
+        <v>-0.1899999999999999</v>
       </c>
       <c r="AA25" t="n">
-        <v>-0.03999999999999998</v>
+        <v>0.09999999999999998</v>
       </c>
       <c r="AB25" t="n">
-        <v>-0.1899999999999999</v>
+        <v>-0.2179465217751024</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.09999999999999998</v>
+        <v>0.1379465217751024</v>
       </c>
       <c r="AD25" t="n">
-        <v>-0.2179465217751024</v>
+        <v>0.5736</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.1379465217751024</v>
+        <v>0.652</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.5736</v>
+        <v>-0.0574538660758902</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.652</v>
+        <v>-0.1740883336847883</v>
       </c>
       <c r="AH25" t="n">
-        <v>-0.0574538660758902</v>
+        <v>0.06650771745028544</v>
       </c>
       <c r="AI25" t="n">
-        <v>-0.1740883336847883</v>
+        <v>0.3874</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.06650771745028544</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="AK25" t="n">
-        <v>-0.1964077382738728</v>
+        <v>0.04819277108433728</v>
       </c>
       <c r="AL25" t="n">
-        <v>0.09773643849630864</v>
+        <v>-0.1011307068695776</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.3874</v>
+        <v>0.186046511627907</v>
       </c>
       <c r="AN25" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.4963912912556804</v>
       </c>
       <c r="AO25" t="n">
-        <v>0.04819277108433728</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>-0.1011307068695776</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0.186046511627907</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>-0.1330957978254479</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0.2137640449438205</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0.4963912912556804</v>
-      </c>
-      <c r="AU25" t="n">
         <v>0.4963912912556804</v>
       </c>
     </row>
@@ -4346,78 +3884,60 @@
         <v>0.109845890390765</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.06604263079909535</v>
+        <v>0.4204</v>
       </c>
       <c r="X26" t="n">
-        <v>0.126298232517028</v>
+        <v>0.4204</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.4204</v>
+        <v>0.009999999999999953</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.4204</v>
+        <v>-0.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.009999999999999953</v>
+        <v>0.13</v>
       </c>
       <c r="AB26" t="n">
-        <v>-0.1</v>
+        <v>-0.1300000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="AD26" t="n">
-        <v>-0.1300000000000001</v>
+        <v>0.8988</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.15</v>
+        <v>0.9298</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.8988</v>
+        <v>0.05032872807573235</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.9298</v>
+        <v>-0.02442353779303608</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.05032872807573235</v>
+        <v>0.1190042416985165</v>
       </c>
       <c r="AI26" t="n">
-        <v>-0.02442353779303608</v>
+        <v>0.2234</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.1190042416985165</v>
+        <v>0.2534</v>
       </c>
       <c r="AK26" t="n">
-        <v>-0.04198344604441557</v>
+        <v>-0.02469135802469136</v>
       </c>
       <c r="AL26" t="n">
-        <v>0.1337191928737621</v>
+        <v>-0.1538461538461539</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.2234</v>
+        <v>0.0975609756097561</v>
       </c>
       <c r="AN26" t="n">
-        <v>0.2534</v>
+        <v>0.6970645323243819</v>
       </c>
       <c r="AO26" t="n">
-        <v>-0.02469135802469136</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>-0.1538461538461539</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0.0975609756097561</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>-0.1832702551163442</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>0.1309523809523809</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0.6970645323243819</v>
-      </c>
-      <c r="AU26" t="n">
         <v>0.6970645323243819</v>
       </c>
     </row>
@@ -4495,78 +4015,60 @@
         <v>0.01684426529898306</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.2310438344457044</v>
+        <v>0.1042</v>
       </c>
       <c r="X27" t="n">
-        <v>0.04152142909993667</v>
+        <v>0.2</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.1042</v>
+        <v>-0.13</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.2</v>
+        <v>-0.24</v>
       </c>
       <c r="AA27" t="n">
-        <v>-0.13</v>
+        <v>0.01000000000000001</v>
       </c>
       <c r="AB27" t="n">
-        <v>-0.24</v>
+        <v>-0.2811437681985129</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.01000000000000001</v>
+        <v>0.02114376819851288</v>
       </c>
       <c r="AD27" t="n">
-        <v>-0.2811437681985129</v>
+        <v>0.096</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.02114376819851288</v>
+        <v>0.096</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.096</v>
+        <v>-0.09452473348763302</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.096</v>
+        <v>-0.197960917872517</v>
       </c>
       <c r="AH27" t="n">
-        <v>-0.09452473348763302</v>
+        <v>0.01803340774033444</v>
       </c>
       <c r="AI27" t="n">
-        <v>-0.197960917872517</v>
+        <v>0.1464</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.01803340774033444</v>
+        <v>0.2534</v>
       </c>
       <c r="AK27" t="n">
-        <v>-0.2277087488248055</v>
+        <v>0.07407407407407407</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.04013349291835427</v>
+        <v>-0.06851676901275384</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.1464</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="AN27" t="n">
-        <v>0.2534</v>
+        <v>0.3183635018592356</v>
       </c>
       <c r="AO27" t="n">
-        <v>0.07407407407407407</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>-0.06851676901275384</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0.2195121951219512</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>-0.1025641025641025</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0.247191011235955</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0.3183635018592356</v>
-      </c>
-      <c r="AU27" t="n">
         <v>0.6367270037184711</v>
       </c>
     </row>
@@ -4644,78 +4146,60 @@
         <v>-0.02041388837447371</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.2618338033782542</v>
+        <v>0.0308</v>
       </c>
       <c r="X28" t="n">
-        <v>-0.00138401426358776</v>
+        <v>0.0712</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.0308</v>
+        <v>-0.14</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.0712</v>
+        <v>-0.24</v>
       </c>
       <c r="AA28" t="n">
-        <v>-0.14</v>
+        <v>-0.01999999999999996</v>
       </c>
       <c r="AB28" t="n">
-        <v>-0.24</v>
+        <v>-0.2729939290125225</v>
       </c>
       <c r="AC28" t="n">
-        <v>-0.01999999999999996</v>
+        <v>-0.007006070987477409</v>
       </c>
       <c r="AD28" t="n">
-        <v>-0.2729939290125225</v>
+        <v>0.0344</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.007006070987477409</v>
+        <v>0.0456</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.0344</v>
+        <v>-0.1448534615633654</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.0456</v>
+        <v>-0.2467096507242682</v>
       </c>
       <c r="AH28" t="n">
-        <v>-0.1448534615633654</v>
+        <v>-0.0381532843719509</v>
       </c>
       <c r="AI28" t="n">
-        <v>-0.2467096507242682</v>
+        <v>0.0166</v>
       </c>
       <c r="AJ28" t="n">
-        <v>-0.0381532843719509</v>
+        <v>0.0416</v>
       </c>
       <c r="AK28" t="n">
-        <v>-0.2664291767358395</v>
+        <v>0.09876543209876543</v>
       </c>
       <c r="AL28" t="n">
-        <v>-0.01398700825553099</v>
+        <v>-0.03531512605042012</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.0166</v>
+        <v>0.225</v>
       </c>
       <c r="AN28" t="n">
-        <v>0.0416</v>
+        <v>0.1417757033000374</v>
       </c>
       <c r="AO28" t="n">
-        <v>0.09876543209876543</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>-0.03531512605042012</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>-0.05952380952380953</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0.253012048192771</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0.1417757033000374</v>
-      </c>
-      <c r="AU28" t="n">
         <v>0.4253271099001121</v>
       </c>
     </row>
@@ -4793,78 +4277,60 @@
         <v>0.06547520468815603</v>
       </c>
       <c r="W29" t="n">
-        <v>-0.09291287180632646</v>
+        <v>0.8854</v>
       </c>
       <c r="X29" t="n">
-        <v>0.08331934941202566</v>
+        <v>0.8854</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.8854</v>
+        <v>0.04499999999999998</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.8854</v>
+        <v>-0.06</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.04499999999999998</v>
+        <v>0.11</v>
       </c>
       <c r="AB29" t="n">
-        <v>-0.06</v>
+        <v>-0.06326585595470137</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.11</v>
+        <v>0.1532658559547013</v>
       </c>
       <c r="AD29" t="n">
-        <v>-0.06326585595470137</v>
+        <v>0.4864</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.1532658559547013</v>
+        <v>0.522</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.4864</v>
+        <v>-0.002706481734333466</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.522</v>
+        <v>-0.07294239696519081</v>
       </c>
       <c r="AH29" t="n">
-        <v>-0.002706481734333466</v>
+        <v>0.06548830383029758</v>
       </c>
       <c r="AI29" t="n">
-        <v>-0.07294239696519081</v>
+        <v>0.9432</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.06548830383029758</v>
+        <v>0.9432</v>
       </c>
       <c r="AK29" t="n">
-        <v>-0.08679847766901636</v>
+        <v>-0.02439024390243894</v>
       </c>
       <c r="AL29" t="n">
-        <v>0.0825815187815391</v>
+        <v>-0.1136363636363636</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.9432</v>
+        <v>0.06329113924050633</v>
       </c>
       <c r="AN29" t="n">
-        <v>0.9432</v>
+        <v>0.5957539652373216</v>
       </c>
       <c r="AO29" t="n">
-        <v>-0.02439024390243894</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>-0.1136363636363636</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0.06329113924050633</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>-0.1358024691358024</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0.08235294117647056</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0.5957539652373216</v>
-      </c>
-      <c r="AU29" t="n">
         <v>0.5957539652373216</v>
       </c>
     </row>
@@ -4942,78 +4408,60 @@
         <v>-0.01078326233245271</v>
       </c>
       <c r="W30" t="n">
-        <v>-0.1630802770908324</v>
+        <v>0.0322</v>
       </c>
       <c r="X30" t="n">
-        <v>0.003420383939837149</v>
+        <v>0.0854</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.0322</v>
+        <v>-0.04000000000000004</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.0854</v>
+        <v>-0.1299999999999999</v>
       </c>
       <c r="AA30" t="n">
-        <v>-0.04000000000000004</v>
+        <v>0.06</v>
       </c>
       <c r="AB30" t="n">
-        <v>-0.1299999999999999</v>
+        <v>-0.1635450996153784</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.06</v>
+        <v>0.08354509961537836</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.1635450996153784</v>
+        <v>0.554</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.08354509961537836</v>
+        <v>0.554</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.554</v>
+        <v>-0.08054934946036824</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.554</v>
+        <v>-0.1491257527854514</v>
       </c>
       <c r="AH30" t="n">
-        <v>-0.08054934946036824</v>
+        <v>-0.0122081919540704</v>
       </c>
       <c r="AI30" t="n">
-        <v>-0.1491257527854514</v>
+        <v>0.0262</v>
       </c>
       <c r="AJ30" t="n">
-        <v>-0.0122081919540704</v>
+        <v>0.0726</v>
       </c>
       <c r="AK30" t="n">
-        <v>-0.1664667070136136</v>
+        <v>0.04878048780487809</v>
       </c>
       <c r="AL30" t="n">
-        <v>0.0007103368055883049</v>
+        <v>-0.08045977011494253</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.0262</v>
+        <v>0.1818736141906876</v>
       </c>
       <c r="AN30" t="n">
-        <v>0.0726</v>
+        <v>0.4695996411712908</v>
       </c>
       <c r="AO30" t="n">
-        <v>0.04878048780487809</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>-0.08045977011494253</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>0.1818736141906876</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>-0.1058823529411764</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>0.2107857672349891</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>0.4695996411712908</v>
-      </c>
-      <c r="AU30" t="n">
         <v>0.5957539652373216</v>
       </c>
     </row>
@@ -5091,78 +4539,60 @@
         <v>0.01441944973035713</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.1879078997121967</v>
+        <v>0.1248</v>
       </c>
       <c r="X31" t="n">
-        <v>0.03578304243033203</v>
+        <v>0.2082</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.1248</v>
+        <v>-0.08500000000000002</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.2082</v>
+        <v>-0.19</v>
       </c>
       <c r="AA31" t="n">
-        <v>-0.08500000000000002</v>
+        <v>0.07025000000000091</v>
       </c>
       <c r="AB31" t="n">
-        <v>-0.19</v>
+        <v>-0.2500000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.07025000000000091</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="AD31" t="n">
-        <v>-0.2500000000000001</v>
+        <v>0.3808</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.3982</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.3808</v>
+        <v>-0.07784286772603477</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.3982</v>
+        <v>-0.1632088228480061</v>
       </c>
       <c r="AH31" t="n">
-        <v>-0.07784286772603477</v>
+        <v>0.01120661411790707</v>
       </c>
       <c r="AI31" t="n">
-        <v>-0.1632088228480061</v>
+        <v>0.1042</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.01120661411790707</v>
+        <v>0.181</v>
       </c>
       <c r="AK31" t="n">
-        <v>-0.1831998283357519</v>
+        <v>0.07317073170731703</v>
       </c>
       <c r="AL31" t="n">
-        <v>0.03134171808034375</v>
+        <v>-0.05</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.1042</v>
+        <v>0.2023809523809524</v>
       </c>
       <c r="AN31" t="n">
-        <v>0.181</v>
+        <v>0.2602029217368357</v>
       </c>
       <c r="AO31" t="n">
-        <v>0.07317073170731703</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0.2023809523809524</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>-0.07692307692307691</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0.2307692307692307</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0.2602029217368357</v>
-      </c>
-      <c r="AU31" t="n">
         <v>0.5957539652373216</v>
       </c>
     </row>
@@ -5240,78 +4670,60 @@
         <v>0.01103192398107171</v>
       </c>
       <c r="W32" t="n">
-        <v>-0.09123869203614128</v>
+        <v>0.1386</v>
       </c>
       <c r="X32" t="n">
-        <v>0.02227937094948718</v>
+        <v>0.2192</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.1386</v>
+        <v>-0.01000000000000001</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.2192</v>
+        <v>-0.09999999999999998</v>
       </c>
       <c r="AA32" t="n">
-        <v>-0.01000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="AB32" t="n">
-        <v>-0.09999999999999998</v>
+        <v>-0.1038971985921918</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.06</v>
+        <v>0.08389719859219173</v>
       </c>
       <c r="AD32" t="n">
-        <v>-0.1038971985921918</v>
+        <v>0.7383999999999999</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.08389719859219173</v>
+        <v>0.865</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.7383999999999999</v>
+        <v>-0.03601433464716919</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.865</v>
+        <v>-0.08128862160672957</v>
       </c>
       <c r="AH32" t="n">
-        <v>-0.03601433464716919</v>
+        <v>0.01090263065652809</v>
       </c>
       <c r="AI32" t="n">
-        <v>-0.08128862160672957</v>
+        <v>0.1346</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.01090263065652809</v>
+        <v>0.2062</v>
       </c>
       <c r="AK32" t="n">
-        <v>-0.09115161458112339</v>
+        <v>0.06763285024154586</v>
       </c>
       <c r="AL32" t="n">
-        <v>0.02135292562963577</v>
+        <v>-0.004830917874396135</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.1346</v>
+        <v>0.1400966183574879</v>
       </c>
       <c r="AN32" t="n">
-        <v>0.2062</v>
+        <v>0.08782509563019504</v>
       </c>
       <c r="AO32" t="n">
-        <v>0.06763285024154586</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>-0.004830917874396135</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>0.1400966183574879</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>-0.01932367149758452</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>0.1594202898550724</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>0.08782509563019504</v>
-      </c>
-      <c r="AU32" t="n">
         <v>0.1756501912603901</v>
       </c>
     </row>
@@ -5389,78 +4801,60 @@
         <v>-0.027652820631649</v>
       </c>
       <c r="W33" t="n">
-        <v>-0.1509793143671761</v>
+        <v>0.004</v>
       </c>
       <c r="X33" t="n">
-        <v>-0.01141466056599728</v>
+        <v>0.0112</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.004</v>
+        <v>-0.06</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.0112</v>
+        <v>-0.15</v>
       </c>
       <c r="AA33" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
         <v>-0.15</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>0.03000000000000003</v>
       </c>
       <c r="AD33" t="n">
-        <v>-0.15</v>
+        <v>0.06</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.03000000000000003</v>
+        <v>0.3396</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.06</v>
+        <v>-0.08522215543724965</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.3396</v>
+        <v>-0.1400943073214456</v>
       </c>
       <c r="AH33" t="n">
-        <v>-0.08522215543724965</v>
+        <v>-0.02918989008947928</v>
       </c>
       <c r="AI33" t="n">
-        <v>-0.1400943073214456</v>
+        <v>0.006</v>
       </c>
       <c r="AJ33" t="n">
-        <v>-0.02918989008947928</v>
+        <v>0.0176</v>
       </c>
       <c r="AK33" t="n">
-        <v>-0.1511909993124803</v>
+        <v>0.111111111111111</v>
       </c>
       <c r="AL33" t="n">
-        <v>-0.01232031333021977</v>
+        <v>0.03381642512077294</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.006</v>
+        <v>0.1835748792270532</v>
       </c>
       <c r="AN33" t="n">
-        <v>0.0176</v>
+        <v>0.006357215082587968</v>
       </c>
       <c r="AO33" t="n">
-        <v>0.111111111111111</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>0.03381642512077294</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>0.1835748792270532</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>0.01932367149758452</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>0.2028985507246377</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>0.006357215082587968</v>
-      </c>
-      <c r="AU33" t="n">
         <v>0.0190716452477639</v>
       </c>
     </row>
@@ -5538,78 +4932,60 @@
         <v>0.01275237325302554</v>
       </c>
       <c r="W34" t="n">
-        <v>-0.123841529568991</v>
+        <v>0.1238</v>
       </c>
       <c r="X34" t="n">
-        <v>0.02673239532361254</v>
+        <v>0.2192</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.1238</v>
+        <v>-0.04999999999999999</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.2192</v>
+        <v>-0.14</v>
       </c>
       <c r="AA34" t="n">
-        <v>-0.04999999999999999</v>
+        <v>0.03000000000000003</v>
       </c>
       <c r="AB34" t="n">
-        <v>-0.14</v>
+        <v>-0.1519260792971538</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.03000000000000003</v>
+        <v>0.05192607929715387</v>
       </c>
       <c r="AD34" t="n">
-        <v>-0.1519260792971538</v>
+        <v>0.2312</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.05192607929715387</v>
+        <v>0.4628</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.2312</v>
+        <v>-0.04920782079008046</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.4628</v>
+        <v>-0.1114327077564689</v>
       </c>
       <c r="AH34" t="n">
-        <v>-0.04920782079008046</v>
+        <v>0.01244135367620838</v>
       </c>
       <c r="AI34" t="n">
-        <v>-0.1114327077564689</v>
+        <v>0.1184</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.01244135367620838</v>
+        <v>0.2062</v>
       </c>
       <c r="AK34" t="n">
-        <v>-0.1228604273873637</v>
+        <v>0.04347826086956519</v>
       </c>
       <c r="AL34" t="n">
-        <v>0.02669462629634852</v>
+        <v>-0.03381642512077294</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.1184</v>
+        <v>0.1159420289855072</v>
       </c>
       <c r="AN34" t="n">
-        <v>0.2062</v>
+        <v>0.3134999455835852</v>
       </c>
       <c r="AO34" t="n">
-        <v>0.04347826086956519</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>-0.03381642512077294</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>0.1159420289855072</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>-0.04830917874396135</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>0.1352657004830918</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0.3134999455835852</v>
-      </c>
-      <c r="AU34" t="n">
         <v>0.3134999455835852</v>
       </c>
     </row>
@@ -5687,78 +5063,60 @@
         <v>0.05394448983572651</v>
       </c>
       <c r="W35" t="n">
-        <v>-0.05453718467014971</v>
+        <v>0.8202</v>
       </c>
       <c r="X35" t="n">
-        <v>0.06313045014530497</v>
+        <v>0.8202</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.8202</v>
+        <v>-0.009999999999999953</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.8202</v>
+        <v>-0.08000000000000002</v>
       </c>
       <c r="AA35" t="n">
-        <v>-0.009999999999999953</v>
+        <v>0.06</v>
       </c>
       <c r="AB35" t="n">
-        <v>-0.08000000000000002</v>
+        <v>-0.09925482790573951</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.06</v>
+        <v>0.07925482790573961</v>
       </c>
       <c r="AD35" t="n">
-        <v>-0.09925482790573951</v>
+        <v>0.7344000000000001</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.07925482790573961</v>
+        <v>0.884</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.7344000000000001</v>
+        <v>0.00759652222489704</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.884</v>
+        <v>-0.04136267558648247</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.00759652222489704</v>
+        <v>0.05592181985989166</v>
       </c>
       <c r="AI35" t="n">
-        <v>-0.04136267558648247</v>
+        <v>0.761</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.05592181985989166</v>
+        <v>0.761</v>
       </c>
       <c r="AK35" t="n">
-        <v>-0.05188362266759158</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>0.06498731161172744</v>
+        <v>-0.07537688442211055</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.761</v>
+        <v>0.07537688442211055</v>
       </c>
       <c r="AN35" t="n">
-        <v>0.761</v>
+        <v>1</v>
       </c>
       <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>-0.07537688442211055</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>0.07537688442211055</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>-0.09547738693467334</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>0.09045226130653261</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU35" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5836,78 +5194,60 @@
         <v>-0.02184629191013983</v>
       </c>
       <c r="W36" t="n">
-        <v>-0.1557722033973963</v>
+        <v>0.0086</v>
       </c>
       <c r="X36" t="n">
-        <v>-0.008380156597759448</v>
+        <v>0.0188</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.0086</v>
+        <v>-0.04999999999999999</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.0188</v>
+        <v>-0.12</v>
       </c>
       <c r="AA36" t="n">
-        <v>-0.04999999999999999</v>
+        <v>0.01999999999999996</v>
       </c>
       <c r="AB36" t="n">
-        <v>-0.12</v>
+        <v>-0.1364378623663955</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.01999999999999996</v>
+        <v>0.03643786236639554</v>
       </c>
       <c r="AD36" t="n">
-        <v>-0.1364378623663955</v>
+        <v>0.1852</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.03643786236639554</v>
+        <v>0.3076</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.1852</v>
+        <v>-0.07762958337910597</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.3076</v>
+        <v>-0.1370381777191459</v>
       </c>
       <c r="AH36" t="n">
-        <v>-0.07762958337910597</v>
+        <v>-0.01531069818067749</v>
       </c>
       <c r="AI36" t="n">
-        <v>-0.1370381777191459</v>
+        <v>0.0224</v>
       </c>
       <c r="AJ36" t="n">
-        <v>-0.01531069818067749</v>
+        <v>0.0424</v>
       </c>
       <c r="AK36" t="n">
-        <v>-0.149432629305434</v>
+        <v>0.04522613065326631</v>
       </c>
       <c r="AL36" t="n">
-        <v>-0.001071822703622701</v>
+        <v>-0.04020100502512563</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.0224</v>
+        <v>0.1306532663316583</v>
       </c>
       <c r="AN36" t="n">
-        <v>0.0424</v>
+        <v>0.3556110610952391</v>
       </c>
       <c r="AO36" t="n">
-        <v>0.04522613065326631</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>-0.04020100502512563</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>0.1306532663316583</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>-0.06030150753768841</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>0.1407035175879398</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>0.3556110610952391</v>
-      </c>
-      <c r="AU36" t="n">
         <v>0.7112221221904782</v>
       </c>
     </row>
@@ -5985,78 +5325,60 @@
         <v>-0.02445697967964856</v>
       </c>
       <c r="W37" t="n">
-        <v>-0.1647937957865656</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="X37" t="n">
-        <v>-0.009124463780871325</v>
+        <v>0.0188</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.04000000000000004</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.0188</v>
+        <v>-0.1</v>
       </c>
       <c r="AA37" t="n">
-        <v>-0.04000000000000004</v>
+        <v>0.03999999999999998</v>
       </c>
       <c r="AB37" t="n">
-        <v>-0.1</v>
+        <v>-0.1300000000000001</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.03999999999999998</v>
+        <v>0.04999999999999998</v>
       </c>
       <c r="AD37" t="n">
-        <v>-0.1300000000000001</v>
+        <v>0.4064</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.04999999999999998</v>
+        <v>0.4548</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.4064</v>
+        <v>-0.08522610560400301</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.4548</v>
+        <v>-0.1485120228288059</v>
       </c>
       <c r="AH37" t="n">
-        <v>-0.08522610560400301</v>
+        <v>-0.01921195482153516</v>
       </c>
       <c r="AI37" t="n">
-        <v>-0.1485120228288059</v>
+        <v>0.0134</v>
       </c>
       <c r="AJ37" t="n">
-        <v>-0.01921195482153516</v>
+        <v>0.0322</v>
       </c>
       <c r="AK37" t="n">
-        <v>-0.1609806360778065</v>
+        <v>0.04522613065326631</v>
       </c>
       <c r="AL37" t="n">
-        <v>-0.003463348309243171</v>
+        <v>-0.04522613065326633</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.0134</v>
+        <v>0.1306532663316583</v>
       </c>
       <c r="AN37" t="n">
-        <v>0.0322</v>
+        <v>0.3619347669211925</v>
       </c>
       <c r="AO37" t="n">
-        <v>0.04522613065326631</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>-0.04522613065326633</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>0.1306532663316583</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>-0.06030150753768848</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>0.1457286432160805</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>0.3619347669211925</v>
-      </c>
-      <c r="AU37" t="n">
         <v>0.7238695338423851</v>
       </c>
     </row>
@@ -6091,13 +5413,13 @@
       <c r="T38" t="n">
         <v>0.006874202420728448</v>
       </c>
-      <c r="AA38" t="n">
+      <c r="Y38" t="n">
         <v>0.03000000000000003</v>
       </c>
-      <c r="AH38" t="n">
+      <c r="AF38" t="n">
         <v>0.02554982389466859</v>
       </c>
-      <c r="AO38" t="n">
+      <c r="AK38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6132,13 +5454,13 @@
       <c r="T39" t="n">
         <v>-0.207727097355152</v>
       </c>
-      <c r="AA39" t="n">
+      <c r="Y39" t="n">
         <v>0.04999999999999999</v>
       </c>
-      <c r="AH39" t="n">
+      <c r="AF39" t="n">
         <v>-0.1505741144926861</v>
       </c>
-      <c r="AO39" t="n">
+      <c r="AK39" t="n">
         <v>0.111111111111111</v>
       </c>
     </row>
@@ -6173,13 +5495,13 @@
       <c r="T40" t="n">
         <v>-0.2146012997758804</v>
       </c>
-      <c r="AA40" t="n">
+      <c r="Y40" t="n">
         <v>0.01999999999999996</v>
       </c>
-      <c r="AH40" t="n">
+      <c r="AF40" t="n">
         <v>-0.1761239383873547</v>
       </c>
-      <c r="AO40" t="n">
+      <c r="AK40" t="n">
         <v>0.111111111111111</v>
       </c>
     </row>
@@ -6214,13 +5536,13 @@
       <c r="T41" t="n">
         <v>-0.2392436043308722</v>
       </c>
-      <c r="AA41" t="n">
+      <c r="Y41" t="n">
         <v>-0.2</v>
       </c>
-      <c r="AH41" t="n">
+      <c r="AF41" t="n">
         <v>-0.1985771734659272</v>
       </c>
-      <c r="AO41" t="n">
+      <c r="AK41" t="n">
         <v>0.07692307692307687</v>
       </c>
     </row>
@@ -6255,13 +5577,13 @@
       <c r="T42" t="n">
         <v>-0.02029213552332382</v>
       </c>
-      <c r="AA42" t="n">
+      <c r="Y42" t="n">
         <v>-0.22</v>
       </c>
-      <c r="AH42" t="n">
+      <c r="AF42" t="n">
         <v>-0.03474506884668338</v>
       </c>
-      <c r="AO42" t="n">
+      <c r="AK42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6296,13 +5618,13 @@
       <c r="T43" t="n">
         <v>0.2189514688075484</v>
       </c>
-      <c r="AA43" t="n">
+      <c r="Y43" t="n">
         <v>-0.01999999999999996</v>
       </c>
-      <c r="AH43" t="n">
+      <c r="AF43" t="n">
         <v>0.1638321046192438</v>
       </c>
-      <c r="AO43" t="n">
+      <c r="AK43" t="n">
         <v>-0.07692307692307687</v>
       </c>
     </row>
@@ -6380,78 +5702,60 @@
         <v>0.1356628677122559</v>
       </c>
       <c r="W44" t="n">
-        <v>-0.03443214233664793</v>
+        <v>0.1438</v>
       </c>
       <c r="X44" t="n">
-        <v>0.156665410712156</v>
+        <v>0.2514</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.1438</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.2514</v>
+        <v>0.005000000000000004</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.005000000000000004</v>
+        <v>-0.01103905938756262</v>
       </c>
       <c r="AC44" t="n">
-        <v>0.15</v>
+        <v>0.1510390593875626</v>
       </c>
       <c r="AD44" t="n">
-        <v>-0.01103905938756262</v>
+        <v>0.046</v>
       </c>
       <c r="AE44" t="n">
-        <v>0.1510390593875626</v>
+        <v>0.1004</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.046</v>
+        <v>0.05929591457575767</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.1004</v>
+        <v>-0.01747428992781219</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.05929591457575767</v>
+        <v>0.1356346254294684</v>
       </c>
       <c r="AI44" t="n">
-        <v>-0.01747428992781219</v>
+        <v>0.1256</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.1356346254294684</v>
+        <v>0.233</v>
       </c>
       <c r="AK44" t="n">
-        <v>-0.0341856494574885</v>
+        <v>-0.1058823529411765</v>
       </c>
       <c r="AL44" t="n">
-        <v>0.1555753535533047</v>
+        <v>-0.1904761904761905</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.1256</v>
+        <v>-0.02298850574712644</v>
       </c>
       <c r="AN44" t="n">
-        <v>0.233</v>
+        <v>0.01875535255227098</v>
       </c>
       <c r="AO44" t="n">
-        <v>-0.1058823529411765</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>-0.1904761904761905</v>
-      </c>
-      <c r="AQ44" t="n">
-        <v>-0.02298850574712644</v>
-      </c>
-      <c r="AR44" t="n">
-        <v>-0.2146021699819167</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT44" t="n">
-        <v>0.01875535255227098</v>
-      </c>
-      <c r="AU44" t="n">
         <v>0.05626605765681295</v>
       </c>
     </row>
@@ -6529,78 +5833,60 @@
         <v>0.04644526155838469</v>
       </c>
       <c r="W45" t="n">
-        <v>-0.1423918378434098</v>
+        <v>0.3514</v>
       </c>
       <c r="X45" t="n">
-        <v>0.06749619072276132</v>
+        <v>0.3514</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.3514</v>
+        <v>-0.03000000000000003</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.3514</v>
+        <v>-0.11</v>
       </c>
       <c r="AA45" t="n">
-        <v>-0.03000000000000003</v>
+        <v>0.06999999999999995</v>
       </c>
       <c r="AB45" t="n">
-        <v>-0.11</v>
+        <v>-0.14</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.06999999999999995</v>
+        <v>0.07999999999999996</v>
       </c>
       <c r="AD45" t="n">
-        <v>-0.14</v>
+        <v>0.7176</v>
       </c>
       <c r="AE45" t="n">
-        <v>0.07999999999999996</v>
+        <v>0.7176</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.7176</v>
+        <v>-0.04230393572236424</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.7176</v>
+        <v>-0.122074903265734</v>
       </c>
       <c r="AH45" t="n">
-        <v>-0.04230393572236424</v>
+        <v>0.04328777221125282</v>
       </c>
       <c r="AI45" t="n">
-        <v>-0.122074903265734</v>
+        <v>0.3518</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.04328777221125282</v>
+        <v>0.3518</v>
       </c>
       <c r="AK45" t="n">
-        <v>-0.1430660495906818</v>
+        <v>0.0235294117647058</v>
       </c>
       <c r="AL45" t="n">
-        <v>0.06534904366984724</v>
+        <v>-0.1059453781512604</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.3518</v>
+        <v>0.1590909090909091</v>
       </c>
       <c r="AN45" t="n">
-        <v>0.3518</v>
+        <v>0.7262668296031756</v>
       </c>
       <c r="AO45" t="n">
-        <v>0.0235294117647058</v>
-      </c>
-      <c r="AP45" t="n">
-        <v>-0.1059453781512604</v>
-      </c>
-      <c r="AQ45" t="n">
-        <v>0.1590909090909091</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>-0.1294117647058824</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>0.1870535714285717</v>
-      </c>
-      <c r="AT45" t="n">
-        <v>0.7262668296031756</v>
-      </c>
-      <c r="AU45" t="n">
         <v>0.7262668296031756</v>
       </c>
     </row>
@@ -6678,78 +5964,60 @@
         <v>-0.008820892249746966</v>
       </c>
       <c r="W46" t="n">
-        <v>-0.2128864519499405</v>
+        <v>0.05</v>
       </c>
       <c r="X46" t="n">
-        <v>0.01240528827111389</v>
+        <v>0.1232</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.1232</v>
+        <v>-0.21</v>
       </c>
       <c r="AA46" t="n">
-        <v>-0.1</v>
+        <v>0.009999999999999957</v>
       </c>
       <c r="AB46" t="n">
-        <v>-0.21</v>
+        <v>-0.2358815227376734</v>
       </c>
       <c r="AC46" t="n">
-        <v>0.009999999999999957</v>
+        <v>0.03588152273767331</v>
       </c>
       <c r="AD46" t="n">
-        <v>-0.2358815227376734</v>
+        <v>0.0872</v>
       </c>
       <c r="AE46" t="n">
-        <v>0.03588152273767331</v>
+        <v>0.116</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.0872</v>
+        <v>-0.1015998502981219</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.116</v>
+        <v>-0.1919855260950264</v>
       </c>
       <c r="AH46" t="n">
-        <v>-0.1015998502981219</v>
+        <v>-0.007528193828980764</v>
       </c>
       <c r="AI46" t="n">
-        <v>-0.1919855260950264</v>
+        <v>0.0482</v>
       </c>
       <c r="AJ46" t="n">
-        <v>-0.007528193828980764</v>
+        <v>0.1208</v>
       </c>
       <c r="AK46" t="n">
-        <v>-0.2108757551997497</v>
+        <v>0.1294117647058823</v>
       </c>
       <c r="AL46" t="n">
-        <v>0.01365533735078727</v>
+        <v>0.02172744273024781</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.0482</v>
+        <v>0.2558139534883721</v>
       </c>
       <c r="AN46" t="n">
-        <v>0.1208</v>
+        <v>0.040303350740512</v>
       </c>
       <c r="AO46" t="n">
-        <v>0.1294117647058823</v>
-      </c>
-      <c r="AP46" t="n">
-        <v>0.02172744273024781</v>
-      </c>
-      <c r="AQ46" t="n">
-        <v>0.2558139534883721</v>
-      </c>
-      <c r="AR46" t="n">
-        <v>-0.01154103180967661</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>0.2790697674418605</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>0.040303350740512</v>
-      </c>
-      <c r="AU46" t="n">
         <v>0.080606701481024</v>
       </c>
     </row>
@@ -6827,78 +6095,60 @@
         <v>-0.01571364885909536</v>
       </c>
       <c r="W47" t="n">
-        <v>-0.1902491681337577</v>
+        <v>0.0342</v>
       </c>
       <c r="X47" t="n">
-        <v>0.004419121202017822</v>
+        <v>0.074</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.0342</v>
+        <v>-0.09999999999999998</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.074</v>
+        <v>-0.29</v>
       </c>
       <c r="AA47" t="n">
-        <v>-0.09999999999999998</v>
+        <v>0.04999999999999999</v>
       </c>
       <c r="AB47" t="n">
-        <v>-0.29</v>
+        <v>-0.3014527242532964</v>
       </c>
       <c r="AC47" t="n">
-        <v>0.04999999999999999</v>
+        <v>0.1014527242532964</v>
       </c>
       <c r="AD47" t="n">
-        <v>-0.3014527242532964</v>
+        <v>0.2748</v>
       </c>
       <c r="AE47" t="n">
-        <v>0.1014527242532964</v>
+        <v>0.5616</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.2748</v>
+        <v>-0.07337409031243958</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.5616</v>
+        <v>-0.1512502880998958</v>
       </c>
       <c r="AH47" t="n">
-        <v>-0.07337409031243958</v>
+        <v>0.007157118637272824</v>
       </c>
       <c r="AI47" t="n">
-        <v>-0.1512502880998958</v>
+        <v>0.0634</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.007157118637272824</v>
+        <v>0.1476</v>
       </c>
       <c r="AK47" t="n">
-        <v>-0.1666264096874345</v>
+        <v>0.1818181818181819</v>
       </c>
       <c r="AL47" t="n">
-        <v>0.02360909830001329</v>
+        <v>0.03571428571428571</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.0634</v>
+        <v>0.3207884097035041</v>
       </c>
       <c r="AN47" t="n">
-        <v>0.1476</v>
+        <v>0.01603078657995181</v>
       </c>
       <c r="AO47" t="n">
-        <v>0.1818181818181819</v>
-      </c>
-      <c r="AP47" t="n">
-        <v>0.03571428571428571</v>
-      </c>
-      <c r="AQ47" t="n">
-        <v>0.3207884097035041</v>
-      </c>
-      <c r="AR47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>0.3559322033898306</v>
-      </c>
-      <c r="AT47" t="n">
-        <v>0.01603078657995181</v>
-      </c>
-      <c r="AU47" t="n">
         <v>0.04809235973985543</v>
       </c>
     </row>
@@ -6976,78 +6226,60 @@
         <v>0.005538385272339627</v>
       </c>
       <c r="W48" t="n">
-        <v>-0.2713462416907573</v>
+        <v>0.0776</v>
       </c>
       <c r="X48" t="n">
-        <v>0.02875608437330033</v>
+        <v>0.121</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.0776</v>
+        <v>-0.04999999999999999</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.121</v>
+        <v>-0.27</v>
       </c>
       <c r="AA48" t="n">
-        <v>-0.04999999999999999</v>
+        <v>0.1299999999999999</v>
       </c>
       <c r="AB48" t="n">
-        <v>-0.27</v>
+        <v>-0.2848860829303957</v>
       </c>
       <c r="AC48" t="n">
-        <v>0.1299999999999999</v>
+        <v>0.1848860829303958</v>
       </c>
       <c r="AD48" t="n">
-        <v>-0.2848860829303957</v>
+        <v>0.6156</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.1848860829303958</v>
+        <v>0.8262</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.6156</v>
+        <v>-0.1285765107759086</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.8262</v>
+        <v>-0.2611673343658558</v>
       </c>
       <c r="AH48" t="n">
-        <v>-0.1285765107759086</v>
+        <v>0.006882814413314898</v>
       </c>
       <c r="AI48" t="n">
-        <v>-0.2611673343658558</v>
+        <v>0.0716</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0.006882814413314898</v>
+        <v>0.1476</v>
       </c>
       <c r="AK48" t="n">
-        <v>-0.293602311461483</v>
+        <v>0.1454545454545455</v>
       </c>
       <c r="AL48" t="n">
-        <v>0.03199705785201198</v>
+        <v>0</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.0716</v>
+        <v>0.2962962962962963</v>
       </c>
       <c r="AN48" t="n">
-        <v>0.1476</v>
+        <v>0.07077063865670001</v>
       </c>
       <c r="AO48" t="n">
-        <v>0.1454545454545455</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>0.2962962962962963</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>-0.03636363636363638</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>0.07077063865670001</v>
-      </c>
-      <c r="AU48" t="n">
         <v>0.1415412773134</v>
       </c>
     </row>
@@ -7125,78 +6357,60 @@
         <v>0.08098219292026777</v>
       </c>
       <c r="W49" t="n">
-        <v>-0.1525470049134301</v>
+        <v>0.624</v>
       </c>
       <c r="X49" t="n">
-        <v>0.1018516267765601</v>
+        <v>0.624</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.624</v>
+        <v>0.04999999999999999</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.624</v>
+        <v>-0.11</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.04999999999999999</v>
+        <v>0.235</v>
       </c>
       <c r="AB49" t="n">
-        <v>-0.11</v>
+        <v>-0.1500107781049751</v>
       </c>
       <c r="AC49" t="n">
-        <v>0.235</v>
+        <v>0.2500107781049751</v>
       </c>
       <c r="AD49" t="n">
-        <v>-0.1500107781049751</v>
+        <v>0.6636</v>
       </c>
       <c r="AE49" t="n">
-        <v>0.2500107781049751</v>
+        <v>0.8262</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.6636</v>
+        <v>-0.05520242046346902</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.8262</v>
+        <v>-0.1806268210664085</v>
       </c>
       <c r="AH49" t="n">
-        <v>-0.05520242046346902</v>
+        <v>0.07217783215824648</v>
       </c>
       <c r="AI49" t="n">
-        <v>-0.1806268210664085</v>
+        <v>0.401</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.07217783215824648</v>
+        <v>0.401</v>
       </c>
       <c r="AK49" t="n">
-        <v>-0.2020535265306768</v>
+        <v>-0.03636363636363638</v>
       </c>
       <c r="AL49" t="n">
-        <v>0.09888569702199178</v>
+        <v>-0.2</v>
       </c>
       <c r="AM49" t="n">
-        <v>0.401</v>
+        <v>0.125</v>
       </c>
       <c r="AN49" t="n">
-        <v>0.401</v>
+        <v>0.6590194421642981</v>
       </c>
       <c r="AO49" t="n">
-        <v>-0.03636363636363638</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AQ49" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>-0.2332457983193273</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>0.1557640297498317</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>0.6590194421642981</v>
-      </c>
-      <c r="AU49" t="n">
         <v>0.6590194421642981</v>
       </c>
     </row>
@@ -7274,78 +6488,60 @@
         <v>0.08615729586757234</v>
       </c>
       <c r="W50" t="n">
-        <v>-0.0745584160310022</v>
+        <v>0.7242</v>
       </c>
       <c r="X50" t="n">
-        <v>0.1060355233978622</v>
+        <v>0.7242</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.7242</v>
+        <v>-0.06999999999999995</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.7242</v>
+        <v>-0.17</v>
       </c>
       <c r="AA50" t="n">
-        <v>-0.06999999999999995</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AB50" t="n">
-        <v>-0.17</v>
+        <v>-0.2183677441315227</v>
       </c>
       <c r="AC50" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.07836774413152281</v>
       </c>
       <c r="AD50" t="n">
-        <v>-0.2183677441315227</v>
+        <v>0.4108</v>
       </c>
       <c r="AE50" t="n">
-        <v>0.07836774413152281</v>
+        <v>0.4366</v>
       </c>
       <c r="AF50" t="n">
-        <v>0.4108</v>
+        <v>0.01491575411360097</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.4366</v>
+        <v>-0.06117732760544649</v>
       </c>
       <c r="AH50" t="n">
-        <v>0.01491575411360097</v>
+        <v>0.08706018702659815</v>
       </c>
       <c r="AI50" t="n">
-        <v>-0.06117732760544649</v>
+        <v>0.7066</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.08706018702659815</v>
+        <v>0.7066</v>
       </c>
       <c r="AK50" t="n">
-        <v>-0.07580599039501187</v>
+        <v>0.0625</v>
       </c>
       <c r="AL50" t="n">
-        <v>0.105424741488038</v>
+        <v>-0.04301075268817205</v>
       </c>
       <c r="AM50" t="n">
-        <v>0.7066</v>
+        <v>0.1735337824450171</v>
       </c>
       <c r="AN50" t="n">
-        <v>0.7066</v>
+        <v>0.2596159410970464</v>
       </c>
       <c r="AO50" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>-0.04301075268817205</v>
-      </c>
-      <c r="AQ50" t="n">
-        <v>0.1735337824450171</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>-0.06619047619047609</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>0.1980198019801981</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>0.2596159410970464</v>
-      </c>
-      <c r="AU50" t="n">
         <v>0.5192318821940929</v>
       </c>
     </row>
@@ -7423,78 +6619,60 @@
         <v>0.03676725420379773</v>
       </c>
       <c r="W51" t="n">
-        <v>-0.1828267188063271</v>
+        <v>0.219</v>
       </c>
       <c r="X51" t="n">
-        <v>0.06005694681439747</v>
+        <v>0.368</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.219</v>
+        <v>-0.09999999999999998</v>
       </c>
       <c r="Z51" t="n">
-        <v>0.368</v>
+        <v>-0.22</v>
       </c>
       <c r="AA51" t="n">
-        <v>-0.09999999999999998</v>
+        <v>0.03000000000000003</v>
       </c>
       <c r="AB51" t="n">
-        <v>-0.22</v>
+        <v>-0.254979020426922</v>
       </c>
       <c r="AC51" t="n">
-        <v>0.03000000000000003</v>
+        <v>0.05497902042692202</v>
       </c>
       <c r="AD51" t="n">
-        <v>-0.254979020426922</v>
+        <v>0.1116</v>
       </c>
       <c r="AE51" t="n">
-        <v>0.05497902042692202</v>
+        <v>0.3012</v>
       </c>
       <c r="AF51" t="n">
-        <v>0.1116</v>
+        <v>-0.0681693671378672</v>
       </c>
       <c r="AG51" t="n">
-        <v>0.3012</v>
+        <v>-0.1626438318502522</v>
       </c>
       <c r="AH51" t="n">
-        <v>-0.0681693671378672</v>
+        <v>0.02681494819153998</v>
       </c>
       <c r="AI51" t="n">
-        <v>-0.1626438318502522</v>
+        <v>0.1842</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0.02681494819153998</v>
+        <v>0.3322</v>
       </c>
       <c r="AK51" t="n">
-        <v>-0.1817470616574172</v>
+        <v>0.09375</v>
       </c>
       <c r="AL51" t="n">
-        <v>0.05034863552625765</v>
+        <v>-0.03225806451612903</v>
       </c>
       <c r="AM51" t="n">
-        <v>0.1842</v>
+        <v>0.2173913043478261</v>
       </c>
       <c r="AN51" t="n">
-        <v>0.3322</v>
+        <v>0.1475811616225303</v>
       </c>
       <c r="AO51" t="n">
-        <v>0.09375</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>-0.03225806451612903</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>0.2173913043478261</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>-0.06060606060606055</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>0.2474226804123711</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>0.1475811616225303</v>
-      </c>
-      <c r="AU51" t="n">
         <v>0.3894239116455697</v>
       </c>
     </row>
@@ -7572,78 +6750,60 @@
         <v>0.01939793490161528</v>
       </c>
       <c r="W52" t="n">
-        <v>-0.1950203783799083</v>
+        <v>0.126</v>
       </c>
       <c r="X52" t="n">
-        <v>0.04253698791876181</v>
+        <v>0.2718</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.126</v>
+        <v>-0.03000000000000003</v>
       </c>
       <c r="Z52" t="n">
-        <v>0.2718</v>
+        <v>-0.2</v>
       </c>
       <c r="AA52" t="n">
-        <v>-0.03000000000000003</v>
+        <v>0.09499999999999997</v>
       </c>
       <c r="AB52" t="n">
-        <v>-0.2</v>
+        <v>-0.21</v>
       </c>
       <c r="AC52" t="n">
-        <v>0.09499999999999997</v>
+        <v>0.15</v>
       </c>
       <c r="AD52" t="n">
-        <v>-0.21</v>
+        <v>0.6028</v>
       </c>
       <c r="AE52" t="n">
-        <v>0.15</v>
+        <v>0.7452</v>
       </c>
       <c r="AF52" t="n">
-        <v>0.6028</v>
+        <v>-0.08308512125146816</v>
       </c>
       <c r="AG52" t="n">
-        <v>0.7452</v>
+        <v>-0.174616748535862</v>
       </c>
       <c r="AH52" t="n">
-        <v>-0.08308512125146816</v>
+        <v>0.01227411693574476</v>
       </c>
       <c r="AI52" t="n">
-        <v>-0.174616748535862</v>
+        <v>0.0892</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0.01227411693574476</v>
+        <v>0.2148</v>
       </c>
       <c r="AK52" t="n">
-        <v>-0.1966963507477006</v>
+        <v>0.03125</v>
       </c>
       <c r="AL52" t="n">
-        <v>0.0358168019290894</v>
+        <v>-0.09090909090909091</v>
       </c>
       <c r="AM52" t="n">
-        <v>0.0892</v>
+        <v>0.1530658209229638</v>
       </c>
       <c r="AN52" t="n">
-        <v>0.2148</v>
+        <v>0.623136721890589</v>
       </c>
       <c r="AO52" t="n">
-        <v>0.03125</v>
-      </c>
-      <c r="AP52" t="n">
-        <v>-0.09090909090909091</v>
-      </c>
-      <c r="AQ52" t="n">
-        <v>0.1530658209229638</v>
-      </c>
-      <c r="AR52" t="n">
-        <v>-0.1222222222222222</v>
-      </c>
-      <c r="AS52" t="n">
-        <v>0.1806363636363643</v>
-      </c>
-      <c r="AT52" t="n">
-        <v>0.623136721890589</v>
-      </c>
-      <c r="AU52" t="n">
         <v>0.623136721890589</v>
       </c>
     </row>
@@ -7721,78 +6881,60 @@
         <v>0.05442835447373051</v>
       </c>
       <c r="W53" t="n">
-        <v>-0.1800641768989542</v>
+        <v>0.4386</v>
       </c>
       <c r="X53" t="n">
-        <v>0.07805306387358701</v>
+        <v>0.4386</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.4386</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="Z53" t="n">
-        <v>0.4386</v>
+        <v>-0.22</v>
       </c>
       <c r="AA53" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.07499999999999996</v>
       </c>
       <c r="AB53" t="n">
-        <v>-0.22</v>
+        <v>-0.2682789023275368</v>
       </c>
       <c r="AC53" t="n">
-        <v>0.07499999999999996</v>
+        <v>0.1282789023275367</v>
       </c>
       <c r="AD53" t="n">
-        <v>-0.2682789023275368</v>
+        <v>0.4716</v>
       </c>
       <c r="AE53" t="n">
-        <v>0.1282789023275367</v>
+        <v>0.5942</v>
       </c>
       <c r="AF53" t="n">
-        <v>0.4716</v>
+        <v>-0.02065700741615617</v>
       </c>
       <c r="AG53" t="n">
-        <v>0.5942</v>
+        <v>-0.1203046944609821</v>
       </c>
       <c r="AH53" t="n">
-        <v>-0.02065700741615617</v>
+        <v>0.0701502594231018</v>
       </c>
       <c r="AI53" t="n">
-        <v>-0.1203046944609821</v>
+        <v>0.6828</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0.0701502594231018</v>
+        <v>0.6828</v>
       </c>
       <c r="AK53" t="n">
-        <v>-0.1385793321652294</v>
+        <v>0.08163265306122458</v>
       </c>
       <c r="AL53" t="n">
-        <v>0.08969260051272306</v>
+        <v>-0.0851063829787234</v>
       </c>
       <c r="AM53" t="n">
-        <v>0.6828</v>
+        <v>0.24</v>
       </c>
       <c r="AN53" t="n">
-        <v>0.6828</v>
+        <v>0.3490586616807677</v>
       </c>
       <c r="AO53" t="n">
-        <v>0.08163265306122458</v>
-      </c>
-      <c r="AP53" t="n">
-        <v>-0.0851063829787234</v>
-      </c>
-      <c r="AQ53" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="AR53" t="n">
-        <v>-0.1233418367346936</v>
-      </c>
-      <c r="AS53" t="n">
-        <v>0.2727272727272728</v>
-      </c>
-      <c r="AT53" t="n">
-        <v>0.3490586616807677</v>
-      </c>
-      <c r="AU53" t="n">
         <v>0.6981173233615354</v>
       </c>
     </row>
@@ -7870,78 +7012,60 @@
         <v>-0.0102556434356195</v>
       </c>
       <c r="W54" t="n">
-        <v>-0.3080453969851983</v>
+        <v>0.0418</v>
       </c>
       <c r="X54" t="n">
-        <v>0.02309988382244871</v>
+        <v>0.116</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.0418</v>
+        <v>-0.15</v>
       </c>
       <c r="Z54" t="n">
-        <v>0.116</v>
+        <v>-0.26</v>
       </c>
       <c r="AA54" t="n">
-        <v>-0.15</v>
+        <v>0.02999999999999997</v>
       </c>
       <c r="AB54" t="n">
-        <v>-0.26</v>
+        <v>-0.34</v>
       </c>
       <c r="AC54" t="n">
-        <v>0.02999999999999997</v>
+        <v>0.03999999999999998</v>
       </c>
       <c r="AD54" t="n">
-        <v>-0.34</v>
+        <v>0.144</v>
       </c>
       <c r="AE54" t="n">
-        <v>0.03999999999999998</v>
+        <v>0.144</v>
       </c>
       <c r="AF54" t="n">
-        <v>0.144</v>
+        <v>-0.1467628265968637</v>
       </c>
       <c r="AG54" t="n">
-        <v>0.144</v>
+        <v>-0.2790684466297503</v>
       </c>
       <c r="AH54" t="n">
-        <v>-0.1467628265968637</v>
+        <v>-0.00427535470029889</v>
       </c>
       <c r="AI54" t="n">
-        <v>-0.2790684466297503</v>
+        <v>0.0832</v>
       </c>
       <c r="AJ54" t="n">
-        <v>-0.00427535470029889</v>
+        <v>0.1868</v>
       </c>
       <c r="AK54" t="n">
-        <v>-0.3101133885720148</v>
+        <v>0.1020408163265306</v>
       </c>
       <c r="AL54" t="n">
-        <v>0.03114547674466149</v>
+        <v>-0.0625</v>
       </c>
       <c r="AM54" t="n">
-        <v>0.0832</v>
+        <v>0.2745098039215687</v>
       </c>
       <c r="AN54" t="n">
-        <v>0.1868</v>
+        <v>0.2549329660061562</v>
       </c>
       <c r="AO54" t="n">
-        <v>0.1020408163265306</v>
-      </c>
-      <c r="AP54" t="n">
-        <v>-0.0625</v>
-      </c>
-      <c r="AQ54" t="n">
-        <v>0.2745098039215687</v>
-      </c>
-      <c r="AR54" t="n">
-        <v>-0.1020408163265306</v>
-      </c>
-      <c r="AS54" t="n">
-        <v>0.3066718995290429</v>
-      </c>
-      <c r="AT54" t="n">
-        <v>0.2549329660061562</v>
-      </c>
-      <c r="AU54" t="n">
         <v>0.5235879925211515</v>
       </c>
     </row>
@@ -8019,78 +7143,60 @@
         <v>0.04704079995483577</v>
       </c>
       <c r="W55" t="n">
-        <v>-0.2805330058716881</v>
+        <v>0.1776</v>
       </c>
       <c r="X55" t="n">
-        <v>0.08036657769316924</v>
+        <v>0.3226</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.1776</v>
+        <v>-0.08000000000000002</v>
       </c>
       <c r="Z55" t="n">
-        <v>0.3226</v>
+        <v>-0.2252499999999995</v>
       </c>
       <c r="AA55" t="n">
-        <v>-0.08000000000000002</v>
+        <v>0.16</v>
       </c>
       <c r="AB55" t="n">
-        <v>-0.2252499999999995</v>
+        <v>-0.3328932128682109</v>
       </c>
       <c r="AC55" t="n">
-        <v>0.16</v>
+        <v>0.1728932128682109</v>
       </c>
       <c r="AD55" t="n">
-        <v>-0.3328932128682109</v>
+        <v>0.6452</v>
       </c>
       <c r="AE55" t="n">
-        <v>0.1728932128682109</v>
+        <v>0.6452</v>
       </c>
       <c r="AF55" t="n">
-        <v>0.6452</v>
+        <v>-0.1261058191807076</v>
       </c>
       <c r="AG55" t="n">
-        <v>0.6452</v>
+        <v>-0.2611889085345304</v>
       </c>
       <c r="AH55" t="n">
-        <v>-0.1261058191807076</v>
+        <v>0.01373743713156786</v>
       </c>
       <c r="AI55" t="n">
-        <v>-0.2611889085345304</v>
+        <v>0.1008</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0.01373743713156786</v>
+        <v>0.1916</v>
       </c>
       <c r="AK55" t="n">
-        <v>-0.2923446509553191</v>
+        <v>0.02040816326530603</v>
       </c>
       <c r="AL55" t="n">
-        <v>0.04652450520583686</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="AM55" t="n">
-        <v>0.1008</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="AN55" t="n">
-        <v>0.1916</v>
+        <v>0.8110057319916437</v>
       </c>
       <c r="AO55" t="n">
-        <v>0.02040816326530603</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>-0.1428571428571428</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>0.1818181818181818</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>-0.1888962765957442</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>0.8110057319916437</v>
-      </c>
-      <c r="AU55" t="n">
         <v>0.8110057319916437</v>
       </c>
     </row>
@@ -8168,78 +7274,60 @@
         <v>0.07322723636668658</v>
       </c>
       <c r="W56" t="n">
-        <v>-0.1002735641034931</v>
+        <v>0.8778</v>
       </c>
       <c r="X56" t="n">
-        <v>0.09178850501315557</v>
+        <v>0.8778</v>
       </c>
       <c r="Y56" t="n">
-        <v>0.8778</v>
+        <v>0.01500000000000001</v>
       </c>
       <c r="Z56" t="n">
-        <v>0.8778</v>
+        <v>-0.1249999999999999</v>
       </c>
       <c r="AA56" t="n">
-        <v>0.01500000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="AB56" t="n">
-        <v>-0.1249999999999999</v>
+        <v>-0.1487049476639393</v>
       </c>
       <c r="AC56" t="n">
-        <v>0.13</v>
+        <v>0.1787049476639393</v>
       </c>
       <c r="AD56" t="n">
-        <v>-0.1487049476639393</v>
+        <v>0.9204</v>
       </c>
       <c r="AE56" t="n">
-        <v>0.1787049476639393</v>
+        <v>0.959</v>
       </c>
       <c r="AF56" t="n">
-        <v>0.9204</v>
+        <v>-0.006478196108377077</v>
       </c>
       <c r="AG56" t="n">
-        <v>0.959</v>
+        <v>-0.08485600723247362</v>
       </c>
       <c r="AH56" t="n">
-        <v>-0.006478196108377077</v>
+        <v>0.07273996529338586</v>
       </c>
       <c r="AI56" t="n">
-        <v>-0.08485600723247362</v>
+        <v>0.8702</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0.07273996529338586</v>
+        <v>0.8702</v>
       </c>
       <c r="AK56" t="n">
-        <v>-0.1003998992513357</v>
+        <v>-0.01470588235294112</v>
       </c>
       <c r="AL56" t="n">
-        <v>0.09183167250276419</v>
+        <v>-0.157222222222222</v>
       </c>
       <c r="AM56" t="n">
-        <v>0.8702</v>
+        <v>0.1230874604847208</v>
       </c>
       <c r="AN56" t="n">
-        <v>0.8702</v>
+        <v>0.8369696418868798</v>
       </c>
       <c r="AO56" t="n">
-        <v>-0.01470588235294112</v>
-      </c>
-      <c r="AP56" t="n">
-        <v>-0.157222222222222</v>
-      </c>
-      <c r="AQ56" t="n">
-        <v>0.1230874604847208</v>
-      </c>
-      <c r="AR56" t="n">
-        <v>-0.1935483870967742</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>0.1584286803966443</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>0.8369696418868798</v>
-      </c>
-      <c r="AU56" t="n">
         <v>0.8369696418868798</v>
       </c>
     </row>
@@ -8317,78 +7405,60 @@
         <v>0.004774570197034649</v>
       </c>
       <c r="W57" t="n">
-        <v>-0.1485247262072127</v>
+        <v>0.1082</v>
       </c>
       <c r="X57" t="n">
-        <v>0.01934328109794941</v>
+        <v>0.236</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.1082</v>
+        <v>0.02500000000000002</v>
       </c>
       <c r="Z57" t="n">
-        <v>0.236</v>
+        <v>-0.1</v>
       </c>
       <c r="AA57" t="n">
-        <v>0.02500000000000002</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="AB57" t="n">
         <v>-0.1</v>
       </c>
       <c r="AC57" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.1500000000000001</v>
       </c>
       <c r="AD57" t="n">
-        <v>-0.1</v>
+        <v>0.914</v>
       </c>
       <c r="AE57" t="n">
-        <v>0.1500000000000001</v>
+        <v>0.914</v>
       </c>
       <c r="AF57" t="n">
-        <v>0.914</v>
+        <v>-0.05274823677256391</v>
       </c>
       <c r="AG57" t="n">
-        <v>0.914</v>
+        <v>-0.1202150197472325</v>
       </c>
       <c r="AH57" t="n">
-        <v>-0.05274823677256391</v>
+        <v>0.01572750489279081</v>
       </c>
       <c r="AI57" t="n">
-        <v>-0.1202150197472325</v>
+        <v>0.1536</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0.01572750489279081</v>
+        <v>0.3498</v>
       </c>
       <c r="AK57" t="n">
-        <v>-0.1362684868749702</v>
+        <v>0.02941176470588236</v>
       </c>
       <c r="AL57" t="n">
-        <v>0.03117009689645702</v>
+        <v>-0.09677419354838709</v>
       </c>
       <c r="AM57" t="n">
-        <v>0.1536</v>
+        <v>0.1594202898550725</v>
       </c>
       <c r="AN57" t="n">
-        <v>0.3498</v>
+        <v>0.6576156647026081</v>
       </c>
       <c r="AO57" t="n">
-        <v>0.02941176470588236</v>
-      </c>
-      <c r="AP57" t="n">
-        <v>-0.09677419354838709</v>
-      </c>
-      <c r="AQ57" t="n">
-        <v>0.1594202898550725</v>
-      </c>
-      <c r="AR57" t="n">
-        <v>-0.1213554463554463</v>
-      </c>
-      <c r="AS57" t="n">
-        <v>0.1884057971014493</v>
-      </c>
-      <c r="AT57" t="n">
-        <v>0.6576156647026081</v>
-      </c>
-      <c r="AU57" t="n">
         <v>0.8369696418868798</v>
       </c>
     </row>
@@ -8466,78 +7536,60 @@
         <v>0.03126839932296965</v>
       </c>
       <c r="W58" t="n">
-        <v>-0.1701281639089326</v>
+        <v>0.2724</v>
       </c>
       <c r="X58" t="n">
-        <v>0.04665807286685156</v>
+        <v>0.4042</v>
       </c>
       <c r="Y58" t="n">
-        <v>0.2724</v>
+        <v>0.01000000000000001</v>
       </c>
       <c r="Z58" t="n">
-        <v>0.4042</v>
+        <v>-0.15</v>
       </c>
       <c r="AA58" t="n">
-        <v>0.01000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="AB58" t="n">
-        <v>-0.15</v>
+        <v>-0.1673720895938451</v>
       </c>
       <c r="AC58" t="n">
-        <v>0.11</v>
+        <v>0.1873720895938451</v>
       </c>
       <c r="AD58" t="n">
-        <v>-0.1673720895938451</v>
+        <v>0.9464</v>
       </c>
       <c r="AE58" t="n">
-        <v>0.1873720895938451</v>
+        <v>0.959</v>
       </c>
       <c r="AF58" t="n">
-        <v>0.9464</v>
+        <v>-0.04627004066418683</v>
       </c>
       <c r="AG58" t="n">
-        <v>0.959</v>
+        <v>-0.1325618866215286</v>
       </c>
       <c r="AH58" t="n">
-        <v>-0.04627004066418683</v>
+        <v>0.03639011811366382</v>
       </c>
       <c r="AI58" t="n">
-        <v>-0.1325618866215286</v>
+        <v>0.304</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0.03639011811366382</v>
+        <v>0.455</v>
       </c>
       <c r="AK58" t="n">
-        <v>-0.1510040686935293</v>
+        <v>0.04411764705882348</v>
       </c>
       <c r="AL58" t="n">
-        <v>0.05598611821277169</v>
+        <v>-0.1000724637681158</v>
       </c>
       <c r="AM58" t="n">
-        <v>0.304</v>
+        <v>0.1935483870967742</v>
       </c>
       <c r="AN58" t="n">
-        <v>0.455</v>
+        <v>0.5546806747894537</v>
       </c>
       <c r="AO58" t="n">
-        <v>0.04411764705882348</v>
-      </c>
-      <c r="AP58" t="n">
-        <v>-0.1000724637681158</v>
-      </c>
-      <c r="AQ58" t="n">
-        <v>0.1935483870967742</v>
-      </c>
-      <c r="AR58" t="n">
-        <v>-0.1273943661971829</v>
-      </c>
-      <c r="AS58" t="n">
-        <v>0.2277272727272732</v>
-      </c>
-      <c r="AT58" t="n">
-        <v>0.5546806747894537</v>
-      </c>
-      <c r="AU58" t="n">
         <v>0.8369696418868798</v>
       </c>
     </row>
@@ -8615,78 +7667,60 @@
         <v>0.07810021020129591</v>
       </c>
       <c r="W59" t="n">
-        <v>-0.1514858494870955</v>
+        <v>0.5936</v>
       </c>
       <c r="X59" t="n">
-        <v>0.09782753559574413</v>
+        <v>0.5936</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.5936</v>
+        <v>0.009999999999999953</v>
       </c>
       <c r="Z59" t="n">
-        <v>0.5936</v>
+        <v>-0.21</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.009999999999999953</v>
+        <v>0.185</v>
       </c>
       <c r="AB59" t="n">
-        <v>-0.21</v>
+        <v>-0.238981138424523</v>
       </c>
       <c r="AC59" t="n">
-        <v>0.185</v>
+        <v>0.2589811384245229</v>
       </c>
       <c r="AD59" t="n">
-        <v>-0.238981138424523</v>
+        <v>0.9903999999999999</v>
       </c>
       <c r="AE59" t="n">
-        <v>0.2589811384245229</v>
+        <v>0.9903999999999999</v>
       </c>
       <c r="AF59" t="n">
-        <v>0.9903999999999999</v>
+        <v>-0.02618731313949252</v>
       </c>
       <c r="AG59" t="n">
-        <v>0.9903999999999999</v>
+        <v>-0.1515407181441714</v>
       </c>
       <c r="AH59" t="n">
-        <v>-0.02618731313949252</v>
+        <v>0.0973010013653824</v>
       </c>
       <c r="AI59" t="n">
-        <v>-0.1515407181441714</v>
+        <v>0.6984</v>
       </c>
       <c r="AJ59" t="n">
-        <v>0.0973010013653824</v>
+        <v>0.6984</v>
       </c>
       <c r="AK59" t="n">
-        <v>-0.1799312153612056</v>
+        <v>0.103448275862069</v>
       </c>
       <c r="AL59" t="n">
-        <v>0.1271639213703788</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="AM59" t="n">
-        <v>0.6984</v>
+        <v>0.303030303030303</v>
       </c>
       <c r="AN59" t="n">
-        <v>0.6984</v>
+        <v>0.3674793695410844</v>
       </c>
       <c r="AO59" t="n">
-        <v>0.103448275862069</v>
-      </c>
-      <c r="AP59" t="n">
-        <v>-0.1333333333333333</v>
-      </c>
-      <c r="AQ59" t="n">
-        <v>0.303030303030303</v>
-      </c>
-      <c r="AR59" t="n">
-        <v>-0.1851851851851851</v>
-      </c>
-      <c r="AS59" t="n">
-        <v>0.3333333333333334</v>
-      </c>
-      <c r="AT59" t="n">
-        <v>0.3674793695410844</v>
-      </c>
-      <c r="AU59" t="n">
         <v>0.5731994364676452</v>
       </c>
     </row>
@@ -8764,78 +7798,60 @@
         <v>0.01348170228143098</v>
       </c>
       <c r="W60" t="n">
-        <v>-0.2888871529740871</v>
+        <v>0.1294</v>
       </c>
       <c r="X60" t="n">
-        <v>0.04611672548407766</v>
+        <v>0.3058</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.1294</v>
+        <v>-0.1</v>
       </c>
       <c r="Z60" t="n">
-        <v>0.3058</v>
+        <v>-0.28</v>
       </c>
       <c r="AA60" t="n">
-        <v>-0.1</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="AB60" t="n">
-        <v>-0.28</v>
+        <v>-0.3049999999999999</v>
       </c>
       <c r="AC60" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.1049999999999999</v>
       </c>
       <c r="AD60" t="n">
-        <v>-0.3049999999999999</v>
+        <v>0.3004</v>
       </c>
       <c r="AE60" t="n">
-        <v>0.1049999999999999</v>
+        <v>0.4966</v>
       </c>
       <c r="AF60" t="n">
-        <v>0.3004</v>
+        <v>-0.1235833122439251</v>
       </c>
       <c r="AG60" t="n">
-        <v>0.4966</v>
+        <v>-0.2465943799926645</v>
       </c>
       <c r="AH60" t="n">
-        <v>-0.1235833122439251</v>
+        <v>0.01540307948929544</v>
       </c>
       <c r="AI60" t="n">
-        <v>-0.2465943799926645</v>
+        <v>0.1906</v>
       </c>
       <c r="AJ60" t="n">
-        <v>0.01540307948929544</v>
+        <v>0.4662</v>
       </c>
       <c r="AK60" t="n">
-        <v>-0.2671963451569795</v>
+        <v>0.1724137931034482</v>
       </c>
       <c r="AL60" t="n">
-        <v>0.04366351123371839</v>
+        <v>-0.03846153846153846</v>
       </c>
       <c r="AM60" t="n">
-        <v>0.1906</v>
+        <v>0.3666666666666666</v>
       </c>
       <c r="AN60" t="n">
-        <v>0.4662</v>
+        <v>0.1260387242163478</v>
       </c>
       <c r="AO60" t="n">
-        <v>0.1724137931034482</v>
-      </c>
-      <c r="AP60" t="n">
-        <v>-0.03846153846153846</v>
-      </c>
-      <c r="AQ60" t="n">
-        <v>0.3666666666666666</v>
-      </c>
-      <c r="AR60" t="n">
-        <v>-0.1047413793103444</v>
-      </c>
-      <c r="AS60" t="n">
-        <v>0.4074074074074074</v>
-      </c>
-      <c r="AT60" t="n">
-        <v>0.1260387242163478</v>
-      </c>
-      <c r="AU60" t="n">
         <v>0.3781161726490435</v>
       </c>
     </row>
@@ -8913,78 +7929,60 @@
         <v>0.03804951396138699</v>
       </c>
       <c r="W61" t="n">
-        <v>-0.3000113564051455</v>
+        <v>0.3006</v>
       </c>
       <c r="X61" t="n">
-        <v>0.057757524936925</v>
+        <v>0.452</v>
       </c>
       <c r="Y61" t="n">
-        <v>0.3006</v>
+        <v>-0.11</v>
       </c>
       <c r="Z61" t="n">
-        <v>0.452</v>
+        <v>-0.315</v>
       </c>
       <c r="AA61" t="n">
-        <v>-0.11</v>
+        <v>0.13</v>
       </c>
       <c r="AB61" t="n">
-        <v>-0.315</v>
+        <v>-0.3808459479217775</v>
       </c>
       <c r="AC61" t="n">
-        <v>0.13</v>
+        <v>0.1608459479217775</v>
       </c>
       <c r="AD61" t="n">
-        <v>-0.3808459479217775</v>
+        <v>0.518</v>
       </c>
       <c r="AE61" t="n">
-        <v>0.1608459479217775</v>
+        <v>0.5424</v>
       </c>
       <c r="AF61" t="n">
-        <v>0.518</v>
+        <v>-0.09739599910443258</v>
       </c>
       <c r="AG61" t="n">
-        <v>0.5424</v>
+        <v>-0.2442581439398056</v>
       </c>
       <c r="AH61" t="n">
-        <v>-0.09739599910443258</v>
+        <v>0.0403748013084874</v>
       </c>
       <c r="AI61" t="n">
-        <v>-0.2442581439398056</v>
+        <v>0.2766</v>
       </c>
       <c r="AJ61" t="n">
-        <v>0.0403748013084874</v>
+        <v>0.4662</v>
       </c>
       <c r="AK61" t="n">
-        <v>-0.2759228001061232</v>
+        <v>0.06896551724137928</v>
       </c>
       <c r="AL61" t="n">
-        <v>0.0682241825416994</v>
+        <v>-0.15625</v>
       </c>
       <c r="AM61" t="n">
-        <v>0.2766</v>
+        <v>0.3214285714285715</v>
       </c>
       <c r="AN61" t="n">
-        <v>0.4662</v>
+        <v>0.5731994364676452</v>
       </c>
       <c r="AO61" t="n">
-        <v>0.06896551724137928</v>
-      </c>
-      <c r="AP61" t="n">
-        <v>-0.15625</v>
-      </c>
-      <c r="AQ61" t="n">
-        <v>0.3214285714285715</v>
-      </c>
-      <c r="AR61" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AS61" t="n">
-        <v>0.3846153846153846</v>
-      </c>
-      <c r="AT61" t="n">
-        <v>0.5731994364676452</v>
-      </c>
-      <c r="AU61" t="n">
         <v>0.5731994364676452</v>
       </c>
     </row>
@@ -9045,7 +8043,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mean error Test</t>
+          <t>Mean Error (MPE) Test</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -9057,7 +8055,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mean absolute error Test</t>
+          <t>MAE Test</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -9069,7 +8067,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Root mean squared error Test</t>
+          <t>RMSE Test</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -9081,7 +8079,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Median absolute error Test</t>
+          <t>MedAE Test</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -9093,7 +8091,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SD of the error Test</t>
+          <t>SD Test</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -9105,7 +8103,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Proportion within tolerance Test</t>
+          <t>Proportion Within Tolerance Test</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -9146,7 +8144,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Adjusted for the m = 3 model pairs of each metric within the group (column p_adj_method). Romano-Wolf step-down: Mean error, Mean absolute error, Root mean squared error, Median absolute error, SD of the error; Hommel: Proportion within tolerance</t>
+          <t>Adjusted for the m = 3 model pairs of each metric within the group (column p_adj_method). Romano-Wolf step-down: Mean Error (MPE), MAE, RMSE, MedAE, SD; Hommel: Proportion Within Tolerance</t>
         </is>
       </c>
     </row>
@@ -9158,7 +8156,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Columns 'CI adj' (Estimates: ci_adj_low, ci_adj_high; method in ci_adj_method), adjusted for the m = 3 model pairs of each metric within the group. Romano-Wolf simultaneous (max-|t|): Mean error, Mean absolute error, Median absolute error; Bonferroni (percentile bootstrap): Root mean squared error, SD of the error, Proportion within tolerance. MPE, MAE and MedAE: 95% simultaneous intervals: difference ± c × SE, c = 95% quantile of the largest bootstrap |t| across comparisons (single-step max-|t|, the interval counterpart of Romano-Wolf). RMSE, SD and the proportion within tolerance: percentile interval of the same patient resamples at coverage 1 - 0.05/m (Bonferroni). These Bonferroni-type intervals need not agree with p_adj when p_adj comes from another statistic (Romano-Wolf, Hommel); use more resamples (e.g. 9,999) for their far tails</t>
+          <t>Columns 'CI adj' (Estimates: ci_adj_low, ci_adj_high; method in ci_adj_method), adjusted for the m = 3 model pairs of each metric within the group, for the MPE, MAE and MedAE only: 95% simultaneous intervals: difference ± c × SE, c = 95% quantile of the largest bootstrap |t| across comparisons (single-step max-|t|, the interval counterpart of Romano-Wolf). The RMSE, SD and the proportion within tolerance have no adjusted interval: their adjusted p-values (Romano-Wolf from a different statistic, or Hommel) have no matching interval, so their CIs are unadjusted. fwer_method='bonferroni' gives Bonferroni p-values with matching intervals for every metric</t>
         </is>
       </c>
     </row>
@@ -24515,15 +23513,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q4" t="n">
-        <v>-0.05856576544801699</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.02781683152088923</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -24653,15 +23645,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q6" t="n">
-        <v>-0.05815433485882694</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.02825025172545625</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -24728,15 +23714,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q7" t="n">
-        <v>-0.03189014549308666</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.09762516046213096</v>
-      </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -24953,15 +23933,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q10" t="n">
-        <v>-0.1343146850892963</v>
-      </c>
-      <c r="R10" t="n">
-        <v>-0.03239054644227168</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -25091,15 +24065,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q12" t="n">
-        <v>-0.1324121069898527</v>
-      </c>
-      <c r="R12" t="n">
-        <v>-0.03081160526701515</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -25166,15 +24134,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q13" t="n">
-        <v>0.005016331658291476</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.1509315375982046</v>
-      </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -25391,15 +24353,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q16" t="n">
-        <v>-0.1237607966652774</v>
-      </c>
-      <c r="R16" t="n">
-        <v>-0.01197481543232409</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -25529,15 +24485,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q18" t="n">
-        <v>-0.1227389787054995</v>
-      </c>
-      <c r="R18" t="n">
-        <v>-0.009991811914109227</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -25604,15 +24554,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q19" t="n">
-        <v>-0.0304885234225776</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.1172132467873379</v>
-      </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -25829,15 +24773,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q22" t="n">
-        <v>-0.1396788216727526</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0.107729520460603</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -25967,15 +24905,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q24" t="n">
-        <v>-0.1403678540165528</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0.1052342909195122</v>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -26042,15 +24974,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q25" t="n">
-        <v>-0.1741545893719806</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0.08108108108108114</v>
-      </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -26267,15 +25193,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q28" t="n">
-        <v>-0.144290130626136</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0.08263711906375129</v>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -26405,15 +25325,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q30" t="n">
-        <v>-0.1469898117459688</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0.08947643166486603</v>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -26480,15 +25394,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q31" t="n">
-        <v>-0.1818181818181818</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0.2205882352941176</v>
-      </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -26705,15 +25613,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q34" t="n">
-        <v>-0.1614748457486424</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0.1308031113881423</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -26843,15 +25745,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q36" t="n">
-        <v>-0.1629424849920504</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0.1368814188906857</v>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -26918,15 +25814,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q37" t="n">
-        <v>-0.1050316598824059</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0.2277272727272732</v>
-      </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -27143,15 +26033,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q40" t="n">
-        <v>-0.06924639598959506</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0.04019670930361872</v>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -27281,15 +26165,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q42" t="n">
-        <v>-0.06892480197736342</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0.04023956149928003</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -27356,15 +26234,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q43" t="n">
-        <v>-0.0212179949513163</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0.1483633705869293</v>
-      </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -27581,15 +26453,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q46" t="n">
-        <v>-0.1735680846859624</v>
-      </c>
-      <c r="R46" t="n">
-        <v>-0.02302037088749732</v>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -27719,15 +26585,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q48" t="n">
-        <v>-0.173472335352231</v>
-      </c>
-      <c r="R48" t="n">
-        <v>-0.02353042056685119</v>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -27794,15 +26654,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q49" t="n">
-        <v>0.008498016588532281</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0.1965811965811965</v>
-      </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -28019,15 +26873,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q52" t="n">
-        <v>-0.157354026556972</v>
-      </c>
-      <c r="R52" t="n">
-        <v>-0.01043630456801225</v>
-      </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -28157,15 +27005,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q54" t="n">
-        <v>-0.1571408854458069</v>
-      </c>
-      <c r="R54" t="n">
-        <v>-0.009901327367602573</v>
-      </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -28232,15 +27074,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q55" t="n">
-        <v>-0.0595744680851064</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0.1346938775510204</v>
-      </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -28457,15 +27293,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q58" t="n">
-        <v>-0.08248699381791254</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0.07690294037236957</v>
-      </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -28595,15 +27425,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q60" t="n">
-        <v>-0.07990146932263836</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0.08197885824929078</v>
-      </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -28670,15 +27494,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q61" t="n">
-        <v>-0.08679783950617274</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0.1954022988505747</v>
-      </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -28895,15 +27713,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q64" t="n">
-        <v>-0.1693070518524953</v>
-      </c>
-      <c r="R64" t="n">
-        <v>0.004803821189166998</v>
-      </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -29033,15 +27845,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q66" t="n">
-        <v>-0.1456654566829713</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0.01203820986317321</v>
-      </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -29108,15 +27914,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q67" t="n">
-        <v>-0.0365853658536585</v>
-      </c>
-      <c r="R67" t="n">
-        <v>0.246964415395788</v>
-      </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -29333,15 +28133,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q70" t="n">
-        <v>-0.1979869724170823</v>
-      </c>
-      <c r="R70" t="n">
-        <v>0.03136522528973919</v>
-      </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -29471,15 +28265,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q72" t="n">
-        <v>-0.1725524403691907</v>
-      </c>
-      <c r="R72" t="n">
-        <v>0.03067357666807528</v>
-      </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -29546,15 +28334,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q73" t="n">
-        <v>-0.1115480649188513</v>
-      </c>
-      <c r="R73" t="n">
-        <v>0.2282217477504961</v>
-      </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -29771,15 +28553,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q76" t="n">
-        <v>-0.311327638423632</v>
-      </c>
-      <c r="R76" t="n">
-        <v>0.1914378186031792</v>
-      </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -29909,15 +28685,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q78" t="n">
-        <v>-0.2790465669838161</v>
-      </c>
-      <c r="R78" t="n">
-        <v>0.2041490419357559</v>
-      </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -29984,15 +28754,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q79" t="n">
-        <v>-0.5833333333333334</v>
-      </c>
-      <c r="R79" t="n">
-        <v>0.1538461538461539</v>
-      </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -30209,15 +28973,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q82" t="n">
-        <v>-0.2372463099349515</v>
-      </c>
-      <c r="R82" t="n">
-        <v>0.07899187056949331</v>
-      </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -30347,15 +29105,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q84" t="n">
-        <v>-0.2454668681387699</v>
-      </c>
-      <c r="R84" t="n">
-        <v>0.08248193350504243</v>
-      </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -30422,15 +29174,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q85" t="n">
-        <v>-0.4285714285714285</v>
-      </c>
-      <c r="R85" t="n">
-        <v>0.1818181818181818</v>
-      </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -30647,15 +29393,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q88" t="n">
-        <v>-0.2687390114133278</v>
-      </c>
-      <c r="R88" t="n">
-        <v>0.1469604057978927</v>
-      </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -30785,15 +29525,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q90" t="n">
-        <v>-0.2472378623407762</v>
-      </c>
-      <c r="R90" t="n">
-        <v>0.1578671368505666</v>
-      </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -30860,15 +29594,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q91" t="n">
-        <v>-0.1875</v>
-      </c>
-      <c r="R91" t="n">
-        <v>0.4166666666666667</v>
-      </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -31085,15 +29813,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q94" t="n">
-        <v>-0.1083550707159749</v>
-      </c>
-      <c r="R94" t="n">
-        <v>0.06043735835439246</v>
-      </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -31223,15 +29945,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q96" t="n">
-        <v>-0.1086563941281395</v>
-      </c>
-      <c r="R96" t="n">
-        <v>0.06197333125436442</v>
-      </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -31298,15 +30014,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q97" t="n">
-        <v>-0.08333333333333326</v>
-      </c>
-      <c r="R97" t="n">
-        <v>0.2051282051282051</v>
-      </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -31523,15 +30233,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q100" t="n">
-        <v>-0.1413278015852511</v>
-      </c>
-      <c r="R100" t="n">
-        <v>0.04323238428178902</v>
-      </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -31661,15 +30365,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q102" t="n">
-        <v>-0.1399212818851053</v>
-      </c>
-      <c r="R102" t="n">
-        <v>0.04949602724711644</v>
-      </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -31736,15 +30434,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q103" t="n">
-        <v>-0.1302489177489176</v>
-      </c>
-      <c r="R103" t="n">
-        <v>0.1688311688311689</v>
-      </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -31961,15 +30653,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q106" t="n">
-        <v>-0.1208265528968928</v>
-      </c>
-      <c r="R106" t="n">
-        <v>0.07898282591475339</v>
-      </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -32099,15 +30785,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q108" t="n">
-        <v>-0.120291009253404</v>
-      </c>
-      <c r="R108" t="n">
-        <v>0.08374599188502276</v>
-      </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -32174,15 +30854,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q109" t="n">
-        <v>-0.2105263157894737</v>
-      </c>
-      <c r="R109" t="n">
-        <v>0.1036050156739813</v>
-      </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -32399,15 +31073,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q112" t="n">
-        <v>-0.1584184428614014</v>
-      </c>
-      <c r="R112" t="n">
-        <v>0.02016397923086491</v>
-      </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -32537,15 +31205,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q114" t="n">
-        <v>-0.1542146413536229</v>
-      </c>
-      <c r="R114" t="n">
-        <v>0.02101114622127575</v>
-      </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -32612,15 +31274,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q115" t="n">
-        <v>-0.0609756097560975</v>
-      </c>
-      <c r="R115" t="n">
-        <v>0.2631578947368421</v>
-      </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -32837,15 +31493,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q118" t="n">
-        <v>-0.2447806093301479</v>
-      </c>
-      <c r="R118" t="n">
-        <v>-0.02207038736559981</v>
-      </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -32975,15 +31625,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q120" t="n">
-        <v>-0.2477664215622339</v>
-      </c>
-      <c r="R120" t="n">
-        <v>-0.01865676378003534</v>
-      </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -33050,15 +31694,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q121" t="n">
-        <v>0.01234567901234562</v>
-      </c>
-      <c r="R121" t="n">
-        <v>0.296646646646647</v>
-      </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -33275,15 +31913,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q124" t="n">
-        <v>-0.1959462103310022</v>
-      </c>
-      <c r="R124" t="n">
-        <v>0.06502125025034049</v>
-      </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -33413,15 +32045,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q126" t="n">
-        <v>-0.1967670115452185</v>
-      </c>
-      <c r="R126" t="n">
-        <v>0.06889649485977117</v>
-      </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -33488,15 +32114,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q127" t="n">
-        <v>-0.1392405063291139</v>
-      </c>
-      <c r="R127" t="n">
-        <v>0.225583333333334</v>
-      </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -33713,15 +32333,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q130" t="n">
-        <v>-0.1169046885201632</v>
-      </c>
-      <c r="R130" t="n">
-        <v>0.1036320810743393</v>
-      </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -33851,15 +32465,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q132" t="n">
-        <v>-0.1196438623098647</v>
-      </c>
-      <c r="R132" t="n">
-        <v>0.1015557952472973</v>
-      </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -33926,15 +32534,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q133" t="n">
-        <v>-0.09024514811031653</v>
-      </c>
-      <c r="R133" t="n">
-        <v>0.2080119115144647</v>
-      </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -34151,15 +32753,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q136" t="n">
-        <v>-0.1857605197426813</v>
-      </c>
-      <c r="R136" t="n">
-        <v>0.07124203167295236</v>
-      </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -34289,15 +32885,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q138" t="n">
-        <v>-0.1840609110439013</v>
-      </c>
-      <c r="R138" t="n">
-        <v>0.06269554011537042</v>
-      </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -34364,15 +32954,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q139" t="n">
-        <v>-0.06199845679012332</v>
-      </c>
-      <c r="R139" t="n">
-        <v>0.2709440813362386</v>
-      </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -34589,15 +33173,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q142" t="n">
-        <v>-0.1967235448779499</v>
-      </c>
-      <c r="R142" t="n">
-        <v>0.09497646596266225</v>
-      </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -34727,15 +33305,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q144" t="n">
-        <v>-0.1964077382738728</v>
-      </c>
-      <c r="R144" t="n">
-        <v>0.09773643849630864</v>
-      </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -34802,15 +33374,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q145" t="n">
-        <v>-0.1330957978254479</v>
-      </c>
-      <c r="R145" t="n">
-        <v>0.2137640449438205</v>
-      </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -35027,15 +33593,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q148" t="n">
-        <v>-0.06604263079909535</v>
-      </c>
-      <c r="R148" t="n">
-        <v>0.126298232517028</v>
-      </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -35165,15 +33725,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q150" t="n">
-        <v>-0.04198344604441557</v>
-      </c>
-      <c r="R150" t="n">
-        <v>0.1337191928737621</v>
-      </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -35240,15 +33794,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q151" t="n">
-        <v>-0.1832702551163442</v>
-      </c>
-      <c r="R151" t="n">
-        <v>0.1309523809523809</v>
-      </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -35465,15 +34013,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q154" t="n">
-        <v>-0.2310438344457044</v>
-      </c>
-      <c r="R154" t="n">
-        <v>0.04152142909993667</v>
-      </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -35603,15 +34145,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q156" t="n">
-        <v>-0.2277087488248055</v>
-      </c>
-      <c r="R156" t="n">
-        <v>0.04013349291835427</v>
-      </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -35678,15 +34214,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q157" t="n">
-        <v>-0.1025641025641025</v>
-      </c>
-      <c r="R157" t="n">
-        <v>0.247191011235955</v>
-      </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -35903,15 +34433,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q160" t="n">
-        <v>-0.2618338033782542</v>
-      </c>
-      <c r="R160" t="n">
-        <v>-0.00138401426358776</v>
-      </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -36041,15 +34565,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q162" t="n">
-        <v>-0.2664291767358395</v>
-      </c>
-      <c r="R162" t="n">
-        <v>-0.01398700825553099</v>
-      </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -36116,15 +34634,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q163" t="n">
-        <v>-0.05952380952380953</v>
-      </c>
-      <c r="R163" t="n">
-        <v>0.253012048192771</v>
-      </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -36341,15 +34853,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q166" t="n">
-        <v>-0.09291287180632646</v>
-      </c>
-      <c r="R166" t="n">
-        <v>0.08331934941202566</v>
-      </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -36479,15 +34985,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q168" t="n">
-        <v>-0.08679847766901636</v>
-      </c>
-      <c r="R168" t="n">
-        <v>0.0825815187815391</v>
-      </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -36554,15 +35054,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q169" t="n">
-        <v>-0.1358024691358024</v>
-      </c>
-      <c r="R169" t="n">
-        <v>0.08235294117647056</v>
-      </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -36779,15 +35273,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q172" t="n">
-        <v>-0.1630802770908324</v>
-      </c>
-      <c r="R172" t="n">
-        <v>0.003420383939837149</v>
-      </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -36917,15 +35405,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q174" t="n">
-        <v>-0.1664667070136136</v>
-      </c>
-      <c r="R174" t="n">
-        <v>0.0007103368055883049</v>
-      </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -36992,15 +35474,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q175" t="n">
-        <v>-0.1058823529411764</v>
-      </c>
-      <c r="R175" t="n">
-        <v>0.2107857672349891</v>
-      </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -37217,15 +35693,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q178" t="n">
-        <v>-0.1879078997121967</v>
-      </c>
-      <c r="R178" t="n">
-        <v>0.03578304243033203</v>
-      </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -37355,15 +35825,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q180" t="n">
-        <v>-0.1831998283357519</v>
-      </c>
-      <c r="R180" t="n">
-        <v>0.03134171808034375</v>
-      </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -37430,15 +35894,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q181" t="n">
-        <v>-0.07692307692307691</v>
-      </c>
-      <c r="R181" t="n">
-        <v>0.2307692307692307</v>
-      </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -37637,15 +36095,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q184" t="n">
-        <v>-0.09123869203614128</v>
-      </c>
-      <c r="R184" t="n">
-        <v>0.02227937094948718</v>
-      </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -37775,15 +36227,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q186" t="n">
-        <v>-0.09115161458112339</v>
-      </c>
-      <c r="R186" t="n">
-        <v>0.02135292562963577</v>
-      </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -37844,15 +36290,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q187" t="n">
-        <v>-0.01932367149758452</v>
-      </c>
-      <c r="R187" t="n">
-        <v>0.1594202898550724</v>
-      </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -38051,15 +36491,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q190" t="n">
-        <v>-0.1509793143671761</v>
-      </c>
-      <c r="R190" t="n">
-        <v>-0.01141466056599728</v>
-      </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -38189,15 +36623,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q192" t="n">
-        <v>-0.1511909993124803</v>
-      </c>
-      <c r="R192" t="n">
-        <v>-0.01232031333021977</v>
-      </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -38258,15 +36686,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q193" t="n">
-        <v>0.01932367149758452</v>
-      </c>
-      <c r="R193" t="n">
-        <v>0.2028985507246377</v>
-      </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -38465,15 +36887,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q196" t="n">
-        <v>-0.123841529568991</v>
-      </c>
-      <c r="R196" t="n">
-        <v>0.02673239532361254</v>
-      </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -38603,15 +37019,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q198" t="n">
-        <v>-0.1228604273873637</v>
-      </c>
-      <c r="R198" t="n">
-        <v>0.02669462629634852</v>
-      </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -38672,15 +37082,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q199" t="n">
-        <v>-0.04830917874396135</v>
-      </c>
-      <c r="R199" t="n">
-        <v>0.1352657004830918</v>
-      </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -38879,15 +37283,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q202" t="n">
-        <v>-0.05453718467014971</v>
-      </c>
-      <c r="R202" t="n">
-        <v>0.06313045014530497</v>
-      </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -39017,15 +37415,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q204" t="n">
-        <v>-0.05188362266759158</v>
-      </c>
-      <c r="R204" t="n">
-        <v>0.06498731161172744</v>
-      </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -39086,15 +37478,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q205" t="n">
-        <v>-0.09547738693467334</v>
-      </c>
-      <c r="R205" t="n">
-        <v>0.09045226130653261</v>
-      </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -39293,15 +37679,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q208" t="n">
-        <v>-0.1557722033973963</v>
-      </c>
-      <c r="R208" t="n">
-        <v>-0.008380156597759448</v>
-      </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -39431,15 +37811,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q210" t="n">
-        <v>-0.149432629305434</v>
-      </c>
-      <c r="R210" t="n">
-        <v>-0.001071822703622701</v>
-      </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -39500,15 +37874,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q211" t="n">
-        <v>-0.06030150753768841</v>
-      </c>
-      <c r="R211" t="n">
-        <v>0.1407035175879398</v>
-      </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -39707,15 +38075,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q214" t="n">
-        <v>-0.1647937957865656</v>
-      </c>
-      <c r="R214" t="n">
-        <v>-0.009124463780871325</v>
-      </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -39845,15 +38207,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q216" t="n">
-        <v>-0.1609806360778065</v>
-      </c>
-      <c r="R216" t="n">
-        <v>-0.003463348309243171</v>
-      </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -39914,15 +38270,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q217" t="n">
-        <v>-0.06030150753768848</v>
-      </c>
-      <c r="R217" t="n">
-        <v>0.1457286432160805</v>
-      </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -41759,15 +40109,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q256" t="n">
-        <v>-0.03443214233664793</v>
-      </c>
-      <c r="R256" t="n">
-        <v>0.156665410712156</v>
-      </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -41897,15 +40241,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q258" t="n">
-        <v>-0.0341856494574885</v>
-      </c>
-      <c r="R258" t="n">
-        <v>0.1555753535533047</v>
-      </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -41972,15 +40310,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q259" t="n">
-        <v>-0.2146021699819167</v>
-      </c>
-      <c r="R259" t="n">
-        <v>0</v>
-      </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -42197,15 +40529,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q262" t="n">
-        <v>-0.1423918378434098</v>
-      </c>
-      <c r="R262" t="n">
-        <v>0.06749619072276132</v>
-      </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -42335,15 +40661,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q264" t="n">
-        <v>-0.1430660495906818</v>
-      </c>
-      <c r="R264" t="n">
-        <v>0.06534904366984724</v>
-      </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -42410,15 +40730,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q265" t="n">
-        <v>-0.1294117647058824</v>
-      </c>
-      <c r="R265" t="n">
-        <v>0.1870535714285717</v>
-      </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -42635,15 +40949,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q268" t="n">
-        <v>-0.2128864519499405</v>
-      </c>
-      <c r="R268" t="n">
-        <v>0.01240528827111389</v>
-      </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -42773,15 +41081,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q270" t="n">
-        <v>-0.2108757551997497</v>
-      </c>
-      <c r="R270" t="n">
-        <v>0.01365533735078727</v>
-      </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -42848,15 +41150,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q271" t="n">
-        <v>-0.01154103180967661</v>
-      </c>
-      <c r="R271" t="n">
-        <v>0.2790697674418605</v>
-      </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -43073,15 +41369,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q274" t="n">
-        <v>-0.1902491681337577</v>
-      </c>
-      <c r="R274" t="n">
-        <v>0.004419121202017822</v>
-      </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -43211,15 +41501,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q276" t="n">
-        <v>-0.1666264096874345</v>
-      </c>
-      <c r="R276" t="n">
-        <v>0.02360909830001329</v>
-      </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -43286,15 +41570,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
-      <c r="R277" t="n">
-        <v>0.3559322033898306</v>
-      </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -43511,15 +41789,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q280" t="n">
-        <v>-0.2713462416907573</v>
-      </c>
-      <c r="R280" t="n">
-        <v>0.02875608437330033</v>
-      </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -43649,15 +41921,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q282" t="n">
-        <v>-0.293602311461483</v>
-      </c>
-      <c r="R282" t="n">
-        <v>0.03199705785201198</v>
-      </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -43724,15 +41990,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q283" t="n">
-        <v>-0.03636363636363638</v>
-      </c>
-      <c r="R283" t="n">
-        <v>0.3333333333333333</v>
-      </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -43949,15 +42209,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q286" t="n">
-        <v>-0.1525470049134301</v>
-      </c>
-      <c r="R286" t="n">
-        <v>0.1018516267765601</v>
-      </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -44087,15 +42341,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q288" t="n">
-        <v>-0.2020535265306768</v>
-      </c>
-      <c r="R288" t="n">
-        <v>0.09888569702199178</v>
-      </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -44162,15 +42410,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q289" t="n">
-        <v>-0.2332457983193273</v>
-      </c>
-      <c r="R289" t="n">
-        <v>0.1557640297498317</v>
-      </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -44387,15 +42629,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q292" t="n">
-        <v>-0.0745584160310022</v>
-      </c>
-      <c r="R292" t="n">
-        <v>0.1060355233978622</v>
-      </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -44525,15 +42761,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q294" t="n">
-        <v>-0.07580599039501187</v>
-      </c>
-      <c r="R294" t="n">
-        <v>0.105424741488038</v>
-      </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -44600,15 +42830,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q295" t="n">
-        <v>-0.06619047619047609</v>
-      </c>
-      <c r="R295" t="n">
-        <v>0.1980198019801981</v>
-      </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -44825,15 +43049,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q298" t="n">
-        <v>-0.1828267188063271</v>
-      </c>
-      <c r="R298" t="n">
-        <v>0.06005694681439747</v>
-      </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -44963,15 +43181,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q300" t="n">
-        <v>-0.1817470616574172</v>
-      </c>
-      <c r="R300" t="n">
-        <v>0.05034863552625765</v>
-      </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -45038,15 +43250,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q301" t="n">
-        <v>-0.06060606060606055</v>
-      </c>
-      <c r="R301" t="n">
-        <v>0.2474226804123711</v>
-      </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -45263,15 +43469,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q304" t="n">
-        <v>-0.1950203783799083</v>
-      </c>
-      <c r="R304" t="n">
-        <v>0.04253698791876181</v>
-      </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -45401,15 +43601,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q306" t="n">
-        <v>-0.1966963507477006</v>
-      </c>
-      <c r="R306" t="n">
-        <v>0.0358168019290894</v>
-      </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -45476,15 +43670,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q307" t="n">
-        <v>-0.1222222222222222</v>
-      </c>
-      <c r="R307" t="n">
-        <v>0.1806363636363643</v>
-      </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -45701,15 +43889,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q310" t="n">
-        <v>-0.1800641768989542</v>
-      </c>
-      <c r="R310" t="n">
-        <v>0.07805306387358701</v>
-      </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -45839,15 +44021,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q312" t="n">
-        <v>-0.1385793321652294</v>
-      </c>
-      <c r="R312" t="n">
-        <v>0.08969260051272306</v>
-      </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -45914,15 +44090,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q313" t="n">
-        <v>-0.1233418367346936</v>
-      </c>
-      <c r="R313" t="n">
-        <v>0.2727272727272728</v>
-      </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -46139,15 +44309,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q316" t="n">
-        <v>-0.3080453969851983</v>
-      </c>
-      <c r="R316" t="n">
-        <v>0.02309988382244871</v>
-      </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -46277,15 +44441,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q318" t="n">
-        <v>-0.3101133885720148</v>
-      </c>
-      <c r="R318" t="n">
-        <v>0.03114547674466149</v>
-      </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -46352,15 +44510,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q319" t="n">
-        <v>-0.1020408163265306</v>
-      </c>
-      <c r="R319" t="n">
-        <v>0.3066718995290429</v>
-      </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -46577,15 +44729,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q322" t="n">
-        <v>-0.2805330058716881</v>
-      </c>
-      <c r="R322" t="n">
-        <v>0.08036657769316924</v>
-      </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -46715,15 +44861,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q324" t="n">
-        <v>-0.2923446509553191</v>
-      </c>
-      <c r="R324" t="n">
-        <v>0.04652450520583686</v>
-      </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -46790,15 +44930,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q325" t="n">
-        <v>-0.1888962765957442</v>
-      </c>
-      <c r="R325" t="n">
-        <v>0.22</v>
-      </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -47015,15 +45149,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q328" t="n">
-        <v>-0.1002735641034931</v>
-      </c>
-      <c r="R328" t="n">
-        <v>0.09178850501315557</v>
-      </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -47153,15 +45281,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q330" t="n">
-        <v>-0.1003998992513357</v>
-      </c>
-      <c r="R330" t="n">
-        <v>0.09183167250276419</v>
-      </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -47228,15 +45350,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q331" t="n">
-        <v>-0.1935483870967742</v>
-      </c>
-      <c r="R331" t="n">
-        <v>0.1584286803966443</v>
-      </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -47453,15 +45569,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q334" t="n">
-        <v>-0.1485247262072127</v>
-      </c>
-      <c r="R334" t="n">
-        <v>0.01934328109794941</v>
-      </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -47591,15 +45701,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q336" t="n">
-        <v>-0.1362684868749702</v>
-      </c>
-      <c r="R336" t="n">
-        <v>0.03117009689645702</v>
-      </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -47666,15 +45770,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q337" t="n">
-        <v>-0.1213554463554463</v>
-      </c>
-      <c r="R337" t="n">
-        <v>0.1884057971014493</v>
-      </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -47891,15 +45989,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q340" t="n">
-        <v>-0.1701281639089326</v>
-      </c>
-      <c r="R340" t="n">
-        <v>0.04665807286685156</v>
-      </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -48029,15 +46121,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q342" t="n">
-        <v>-0.1510040686935293</v>
-      </c>
-      <c r="R342" t="n">
-        <v>0.05598611821277169</v>
-      </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -48104,15 +46190,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q343" t="n">
-        <v>-0.1273943661971829</v>
-      </c>
-      <c r="R343" t="n">
-        <v>0.2277272727272732</v>
-      </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -48329,15 +46409,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q346" t="n">
-        <v>-0.1514858494870955</v>
-      </c>
-      <c r="R346" t="n">
-        <v>0.09782753559574413</v>
-      </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -48467,15 +46541,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q348" t="n">
-        <v>-0.1799312153612056</v>
-      </c>
-      <c r="R348" t="n">
-        <v>0.1271639213703788</v>
-      </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -48542,15 +46610,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q349" t="n">
-        <v>-0.1851851851851851</v>
-      </c>
-      <c r="R349" t="n">
-        <v>0.3333333333333334</v>
-      </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -48767,15 +46829,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q352" t="n">
-        <v>-0.2888871529740871</v>
-      </c>
-      <c r="R352" t="n">
-        <v>0.04611672548407766</v>
-      </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -48905,15 +46961,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q354" t="n">
-        <v>-0.2671963451569795</v>
-      </c>
-      <c r="R354" t="n">
-        <v>0.04366351123371839</v>
-      </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -48980,15 +47030,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q355" t="n">
-        <v>-0.1047413793103444</v>
-      </c>
-      <c r="R355" t="n">
-        <v>0.4074074074074074</v>
-      </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -49205,15 +47249,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q358" t="n">
-        <v>-0.3000113564051455</v>
-      </c>
-      <c r="R358" t="n">
-        <v>0.057757524936925</v>
-      </c>
       <c r="S358" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -49343,15 +47381,9 @@
           <t>Romano-Wolf step-down</t>
         </is>
       </c>
-      <c r="Q360" t="n">
-        <v>-0.2759228001061232</v>
-      </c>
-      <c r="R360" t="n">
-        <v>0.0682241825416994</v>
-      </c>
       <c r="S360" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: its Romano-Wolf p-value comes from a different statistic (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
@@ -49418,15 +47450,9 @@
           <t>Hommel</t>
         </is>
       </c>
-      <c r="Q361" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="R361" t="n">
-        <v>0.3846153846153846</v>
-      </c>
       <c r="S361" t="inlineStr">
         <is>
-          <t>Bonferroni (percentile bootstrap)</t>
+          <t>not adjusted: Hommel p-values have no matching interval (the CI is unadjusted; fwer_method='bonferroni' gives matching intervals)</t>
         </is>
       </c>
     </row>
